--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0006.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0006.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Chọn Buff</t>
+          <t>Chọn Hiệu Ứng Tăng Cường</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Chọn Buff</t>
+          <t>Chọn Hiệu Ứng Tăng Cường</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Kích hoạt khả năng nâng cao của Thundering Mephis, gây sát thương đa giai đoạn.</t>
+          <t>Kích hoạt khả năng nâng cao của Thundering Mephis, gây DMG đa giai đoạn.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Kẻ địch bị đánh bại</t>
+          <t>Đã tiêu diệt kẻ địch</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chọn Buff</t>
+          <t>Chọn Hiệu Ứng Tăng Cường</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Kỹ năng bị khóa</t>
+          <t>Kỹ Năng Đã Khóa</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Khi Resonators gây Sát Thương từ Basic Attack, Attack của tất cả thành viên trong đội sẽ tăng 15% trong 3 giây, có thể chồng chất tối đa 3 lần. Thời gian hiệu lực sẽ được làm mới sau mỗi lần chồng chất.</t>
+          <t>Khi Resonator gây Sát Thương từ Đòn Cơ Bản, ATK của tất cả thành viên trong đội sẽ tăng 15% trong 3 giây, có thể chồng chất tối đa 3 lần. Thời gian hiệu lực sẽ được làm mới sau mỗi lần chồng chất.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Intro Skill, Tấn Công của tất cả thành viên trong đội tăng 8% trong 15 giây, có thể chồng chất tối đa 5 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất mới.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Intro, ATK của tất cả thành viên trong đội tăng 8% trong 15 giây, có thể chồng chất tối đa 5 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất mới.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Resonators nhận thêm 30% Sát Thương Resonance Skill. Khi sử dụng Resonance Skill, Tấn Công tăng 25% trong 4 giây.</t>
+          <t>Resonator nhận thêm 30% Sát Thương Resonance Skill. Khi sử dụng Resonance Skill, ATK tăng 25% trong 4 giây.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Khi bất kỳ Resonator nào nhận hồi máu, Tấn Công của tất cả thành viên trong đội tăng 10%, Crit. DMG tăng 20%, và Energy Regen tăng 30% trong 12 giây.</t>
+          <t>Khi bất kỳ Resonator nào nhận hồi máu, ATK của tất cả thành viên trong đội tăng 10%, Crit. DMG tăng 20%, và Hồi Năng Lượng tăng 30% trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Liberation, Attack của họ tăng 20%, và họ nhận thêm 40% thưởng Sát Thương Heavy Attack trong 15 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.</t>
+          <t>Khi Resonator kích hoạt Resonance Liberation, ATK của họ tăng 20%, và họ nhận thêm 40% thưởng Sát Thương Đòn Nặng trong 15 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Khi Resonators hồi máu cho đồng đội, Tốc Độ Energy Regen của họ sẽ tăng 20% trong 4 giây. Khi Resonators được hồi máu, Crit. DMG của họ sẽ tăng 30% trong 4 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.</t>
+          <t>Khi Resonator hồi máu cho đồng đội, Tốc Độ Hồi Năng Lượng của họ sẽ tăng 20% trong 4 giây. Khi Resonator được hồi máu, Crit. DMG của họ sẽ tăng 30% trong 4 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Skill, Tấn Công của họ tăng 10%, và họ nhận thêm 20% thưởng Sát Thương Resonance Liberation trong 4 giây, có thể chồng chất tối đa 2 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất.</t>
+          <t>Khi Resonator kích hoạt Resonance Skill, ATK của họ tăng 10%, và họ nhận thêm 20% thưởng Sát Thương Resonance Liberation trong 4 giây, có thể chồng chất tối đa 2 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Intro Skill, Crit. DMG của họ tăng 20%, và họ nhận thêm 40% sát thương Basic Attack trong 18 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Intro, Crit. DMG của họ tăng 20%, và họ nhận thêm 40% DMG Đòn Basic Attack trong 18 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Intro Skill, Tấn Công và sát thương gây ra của tất cả thành viên trong đội tăng 5% trong 20 giây, có thể chồng chất tối đa 3 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất mới.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Intro, ATK và DMG gây ra của tất cả thành viên trong đội tăng 5% trong 20 giây, có thể chồng chất tối đa 3 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất mới.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Intro Skill, Tấn Công của họ tăng 5% mỗi giây, có thể chồng chất tối đa 4 lần. Khi đạt tối đa, họ nhận thêm 40% sát thương Resonance Skill Bonus. Hiệu ứng sẽ biến mất khi Resonators rời khỏi chiến trường.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Intro, ATK của họ tăng 5% mỗi giây, có thể chồng chất tối đa 4 lần. Khi đạt tối đa, họ nhận thêm 40% DMG Resonance Skill Bonus. Hiệu ứng sẽ biến mất khi Resonator rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Skill, Tấn Công của họ tăng 20% trong 7 giây, có thể chồng chất tối đa 2 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất.</t>
+          <t>Khi Resonator kích hoạt Resonance Skill, ATK của họ tăng 20% trong 7 giây, có thể chồng chất tối đa 2 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất.</t>
         </is>
       </c>
     </row>
@@ -1876,9 +1876,9 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>&lt;color=#9656d8&gt;"Electro"&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; với &lt;color=#9656d8&gt;Electro DMG&lt;/color&gt;.
-Tacet Field nơi Thundering Mephis trú ngụ. Khu vực này chứa năng lượng Điện cực mạnh do ảnh hưởng của nó. Vì vậy, hãy cẩn thận với tĩnh điện và... tóc của bạn khi chiến đấu ở đây.</t>
+          <t>&lt;color=#9656d8&gt;"Điện"&lt;/color&gt;
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; với &lt;color=#9656d8&gt;Sát Thương Điện&lt;/color&gt;.
+Tổ Tacet nơi Thundering Mephis trú ngụ. Khu vực này chứa năng lượng Điện cực mạnh do ảnh hưởng của nó. Vì vậy, hãy cẩn thận với tĩnh điện và... tóc của bạn khi chiến đấu ở đây.</t>
         </is>
       </c>
     </row>
@@ -1946,8 +1946,8 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>&lt;color=#e15226&gt;"Fusion"&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#e15226&gt;Fusion DMG&lt;/color&gt;.
-Tacet Field nơi Inferno Rider trú ngụ. Nơi đây có một quần thể Incinero Petals khổng lồ, một trong những nguồn năng lượng Fusion chính của khu vực. Nó không chỉ gây nhiễu cảm biến mà còn ảnh hưởng đến tinh thần của Resonators, gây ra ảo giác. Bạn nên trang bị đồ bảo hộ trước khi tiến vào.&lt;/color&gt;</t>
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#e15226&gt;Sát Thương Fusion&lt;/color&gt;.
+Tổ Tacet nơi Inferno Rider trú ngụ. Nơi đây có một quần thể Incinero Petals khổng lồ, một trong những nguồn năng lượng Fusion chính của khu vực. Nó không chỉ gây nhiễu cảm biến mà còn ảnh hưởng đến tinh thần của Resonator, gây ra ảo giác. Bạn nên trang bị đồ bảo hộ trước khi tiến vào.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2015,8 +2015,8 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Mục tiêu có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;.
-Tacet Field nơi Crownless - Avatar trú ngụ. Nồng độ Wutheron cực cao với hoạt động bất ổn được phát hiện tại đây. Được cho là kết quả của các đặc tính nghịch lý mà chính Tacet Discord này thể hiện. Khuyến cáo tránh xa khu vực này. Nếu cần thiết, hãy sơ tán ngay đến Resonance Beacon gần nhất.</t>
+Mục tiêu có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;.
+Tổ Tacet nơi Crownless - Avatar trú ngụ. Nồng độ Wutheron cực cao với hoạt động bất ổn được phát hiện tại đây. Được cho là kết quả của các đặc tính nghịch lý mà chính Tacet Discord này thể hiện. Khuyến cáo tránh xa khu vực này. Nếu cần thiết, hãy sơ tán ngay đến Điểm Cộng Hưởng gần nhất.</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Sử dụng Intro Skill để tạo ra những vụ nổ mạnh, gây sát thương lên tất cả kẻ địch trong phạm vi xung quanh.</t>
+          <t>Sử dụng Kỹ Năng Khởi Động để tạo ra những vụ nổ mạnh, gây sát thương lên tất cả kẻ địch trong phạm vi xung quanh.</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Dodge tránh giải phóng Sấm Nước Styx, gây Electro DMG lên tất cả kẻ địch trong phạm vi rộng.</t>
+          <t>Né tránh giải phóng Sấm Nước Styx, gây Sát Thương Electro lên tất cả kẻ địch trong phạm vi rộng.</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Tạo liên tục các Quả Cầu Năng Lượng Gió. Thu thập chúng để hồi phục STA và tăng Aero DMG cho Đòn Tấn Công Nặng và Đòn Lao Xuống.</t>
+          <t>Tạo liên tục các Quả Cầu Năng Lượng Gió. Thu thập chúng để hồi phục STA và tăng Sát Thương Aero cho Đòn Tấn Công Nặng và Đòn Lao Xuống.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>Quả Cầu Năng Lượng Zephyr giờ đây sẽ cấp trạng thái Zephyr có thể chồng chất.
-Trạng thái Zephyr cho phép nhân vật gây thêm Aero DMG 1 lần trong Đòn Tấn Công Nặng và Đòn Lao Xuống.</t>
+Trạng thái Zephyr cho phép nhân vật gây thêm Sát Thương Aero 1 lần trong Đòn Heavy Attack và Đòn Lao Xuống.</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Liên tục tạo ra Quả Cầu Năng Lượng Nổ. Khi thu thập một Quả Cầu Năng Lượng Nổ, Resonance Skill tiếp theo của bạn sẽ tạo ra Vùng Lửa kéo dài 3 giây, gây Fusion DMG liên tục.</t>
+          <t>Liên tục tạo ra Quả Cầu Năng Lượng Nổ. Khi thu thập một Quả Cầu Năng Lượng Nổ, Resonance Skill tiếp theo của bạn sẽ tạo ra Vùng Lửa kéo dài 3 giây, gây sát thương Fusion liên tục.</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Sau khi nhặt được Quả Cầu Năng Lượng Nổ, sẽ gây thêm Fusion DMG cho kẻ địch xung quanh 1 lần trước khi tạo ra Vùng Lửa.</t>
+          <t>Sau khi nhặt được Quả Cầu Năng Lượng Nổ, sẽ gây thêm Sát Thương Fusion cho kẻ địch xung quanh 1 lần trước khi tạo ra Vùng Lửa.</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Tăng hiệu quả hồi phục và hồi phục nhận vào. Mỗi đòn tấn công gây thêm Aero DMG khi HP của nhân vật trên 80%.</t>
+          <t>Tăng hiệu quả hồi phục và hồi phục nhận vào. Mỗi đòn tấn công gây thêm Sát Thương Aero khi HP của nhân vật trên 80%.</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Khi Character có lượng HP trên 80%, Heavy Attack sẽ tạo ra một Vòng Xoáy Lớn (Cooldown chiêu 1,5 giây).</t>
+          <t>Khi Nhân Vật có lượng HP trên 80%, Đòn Heavy Attack sẽ tạo ra một Vòng Xoáy Lớn (thời gian hồi chiêu 1,5 giây).</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Liên tục tạo ra Quả Cầu Năng Lượng Băng. Trong 3 giây đầu sau khi nhặt, Basic Attack và Heavy Attack của bạn sẽ đóng băng kẻ địch.</t>
+          <t>Liên tục tạo ra Quả Cầu Năng Lượng Băng. Trong 3 giây đầu sau khi nhặt, Đòn Basic Attack và Đòn Tấn Công Mạnh của bạn sẽ đóng băng kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Các Quả cầu Năng lượng Băng giờ đây sẽ đóng băng kẻ địch trong phạm vi rộng hơn khi sử dụng Kỹ năng Cơ bản hoặc Tấn công Nặng. Resonator cũng sẽ gây thêm sát thương lên kẻ địch bị đóng băng.</t>
+          <t>Các Quả cầu Năng lượng Băng giờ đây sẽ đóng băng kẻ địch trong phạm vi rộng hơn khi sử dụng Kỹ năng Cơ bản hoặc Tấn công Nặng. Cộng Hưởng Giả cũng sẽ gây thêm sát thương lên kẻ địch bị đóng băng.</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Chính: DEF%</t>
+          <t>Chính: Phòng Ngự%</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Chủ: Sát Thương Physical+</t>
+          <t>Chủ: Sát Thương Vật Lý+</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Phụ: ATK</t>
+          <t>ATK</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Phụ: ATK%</t>
+          <t>ATK%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Phụ: DEF%</t>
+          <t>Phòng Ngự%</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Phụ: Tỉ lệ Crit</t>
+          <t>Crit. Rate</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Phụ: Sát thương Crit</t>
+          <t>Crit. DMG</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Chính: Glacio DMG+</t>
+          <t>Chính: Sát Thương Glacio+</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Chính: Fusion DMG+</t>
+          <t>Chính: Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Phụ: Sát Thương Physical+</t>
+          <t>Phụ: Sát Thương Vật Lý+</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Chính: Electro DMG+</t>
+          <t>Chính: Sát Thương Electro+</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Chính: Aero DMG+</t>
+          <t>Chính: Sát Thương Aero+</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Chính: Spectro DMG+</t>
+          <t>Chủ: Sát Thương Spectro+</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Chính: Havoc DMG+</t>
+          <t>Chủ: Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Phụ: Glacio DMG+</t>
+          <t>Sát Thương Glacio+</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Phụ: Fusion DMG+</t>
+          <t>Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Phụ: Electro DMG+</t>
+          <t>Sát Thương Electro+</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Phụ: Aero DMG+</t>
+          <t>Sát Thương Aero+</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Phụ: Spectro DMG+</t>
+          <t>Phụ: Sát Thương Spectro+</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Phụ: Havoc DMG+</t>
+          <t>Phụ: Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Sort theo HP Tối Đa</t>
+          <t>Sắp xếp theo HP Tối Đa</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Sort theo Tấn Công</t>
+          <t>Sắp xếp theo ATK</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Sort theo Phòng Ngự</t>
+          <t>Sắp xếp theo Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Chính: ATK</t>
+          <t>ATK:</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Phụ: Sát Thương Resonance Skill+</t>
+          <t>Phụ: Sát Thương Kỹ Năng Cộng Hưởng+</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Phụ: DMG Basic Attack+</t>
+          <t>Sát Thương Kỹ Năng Cơ Bản+</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Phụ: DMG Heavy Attack+</t>
+          <t>Phụ: Sát Thương Bạo Kích+</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Phụ: Sát Thương Resonance Liberation+</t>
+          <t>Phụ: Sát Thương Giải Phóng Cộng Hưởng+</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Tấn Công%</t>
+          <t>ATK%</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>PHÒNG NGỤ</t>
+          <t>DEF</t>
         </is>
       </c>
     </row>
@@ -5726,10 +5726,10 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Five Thunders Spell Array&lt;/color&gt; kích hoạt, tất cả Resonators trong đội sẽ bước vào trạng thái &lt;color=Highlight&gt;Thunder Spell - Primordial Qi&lt;/color&gt;.
-- Trong trạng thái &lt;color=Highlight&gt;Thunder Spell - Primordial Qi&lt;/color&gt;, khi bất kỳ Resonators nào trong đội sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt;, &lt;color=Highlight&gt;Thunder Spell - Primordial Qi&lt;/color&gt; sẽ chuyển thành &lt;color=Highlight&gt;Thunder Spell - Yin and Yang&lt;/color&gt;.
-- &lt;color=Highlight&gt;Thunder Spell - Yin and Yang&lt;/color&gt; tăng {0} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; cho Resonators đang hoạt động trong đội. Khi bất kỳ Resonators nào trong đội sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; trong trạng thái này, &lt;color=Highlight&gt;Thunder Spell - Yin and Yang&lt;/color&gt; sẽ chuyển thành &lt;color=Highlight&gt;Thunder Spell - Heaven, Earth, Mind&lt;/color&gt;.
-- &lt;color=Highlight&gt;Thunder Spell - Heaven, Earth, Mind&lt;/color&gt; tăng {1} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; cho Resonators đang hoạt động trong đội.</t>
+          <t>Khi &lt;color=Highlight&gt;Bát Quái Trận Đồ Ngũ Lôi&lt;/color&gt; kích hoạt, tất cả Resonator trong đội sẽ bước vào trạng thái &lt;color=Highlight&gt;Thần Lôi - Nguyên Khí&lt;/color&gt;.
+- Trong trạng thái &lt;color=Highlight&gt;Thần Lôi - Nguyên Khí&lt;/color&gt;, khi bất kỳ Resonator nào trong đội sử dụng &lt;color=Highlight&gt;Kỹ Năng Nhập Môn&lt;/color&gt;, &lt;color=Highlight&gt;Thần Lôi - Nguyên Khí&lt;/color&gt; sẽ chuyển thành &lt;color=Highlight&gt;Thần Lôi - Âm Dương&lt;/color&gt;.
+- &lt;color=Highlight&gt;Thần Lôi - Âm Dương&lt;/color&gt; tăng {0} &lt;color=Highlight&gt;Sát Thương Resonance Skill&lt;/color&gt; cho Resonator đang hoạt động trong đội. Khi bất kỳ Resonator nào trong đội sử dụng &lt;color=Highlight&gt;Kỹ Năng Nhập Môn&lt;/color&gt; trong trạng thái này, &lt;color=Highlight&gt;Thần Lôi - Âm Dương&lt;/color&gt; sẽ chuyển thành &lt;color=Highlight&gt;Thần Lôi - Thiên Địa Tâm&lt;/color&gt;.
+- &lt;color=Highlight&gt;Thần Lôi - Thiên Địa Tâm&lt;/color&gt; tăng {1} &lt;color=Highlight&gt;Sát Thương Resonance Skill&lt;/color&gt; cho Resonator đang hoạt động trong đội.</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Khi Resonators thực hiện Đòn Tấn Công Thường, một cơn lốc sẽ xuất hiện quanh mục tiêu, gây Sát Thương Khu Vực không thuộc tính. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây.</t>
+          <t>Khi Resonator thực hiện Đòn Normal Attack, một cơn lốc sẽ xuất hiện quanh mục tiêu, gây Sát Thương Khu Vực không thuộc tính. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Khi Resonators gây sát thương lên một mục tiêu, mục tiêu sẽ chịu Sát Thương &lt;color=Fire&gt;Fusion&lt;/color&gt; tương đương 0,05% HP tối đa mỗi giây trong 12 giây.</t>
+          <t>Khi Resonator gây DMG lên một mục tiêu, mục tiêu sẽ chịu Sát Thương &lt;color=Fire&gt;Fusion&lt;/color&gt; tương đương 0,05% HP tối đa mỗi giây trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation sẽ tăng 20% Sát Thương toàn đội trong 12 giây và giảm 15% Aero RES DMG và Electro RES DMG của tất cả kẻ địch.</t>
+          <t>Kích hoạt Resonance Liberation sẽ tăng 20% Sát Thương toàn đội trong 12 giây và giảm 15% Kháng Sát Thương Aero và Kháng Sát Thương Electro của tất cả kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Khi Dodge thành công, Crit. Rate tăng 20% trong 8 giây, tối đa 3 lần cộng dồn. Thời gian hiệu ứng sẽ được làm mới với mỗi lần cộng dồn mới.</t>
+          <t>Khi Né Tránh thành công, Crit. Rate tăng 20% trong 8 giây, tối đa 3 lần cộng dồn. Thời gian hiệu ứng sẽ được làm mới với mỗi lần cộng dồn mới.</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Resonators nhận 30% &lt;color=Thunder&gt;Electro DMG Bonus&lt;/color&gt;.</t>
+          <t>Resonator nhận 30% &lt;color=Thunder&gt;Tăng Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Resonators nhận 30% &lt;color=Wind&gt;Aero DMG Bonus&lt;/color&gt;.</t>
+          <t>Resonator nhận 30% &lt;color=Wind&gt;Tăng Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Resonators nhận 30% &lt;color=Fire&gt;Fusion DMG Bonus&lt;/color&gt;.</t>
+          <t>Resonator nhận 30% &lt;color=Fire&gt;Tăng Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Resonators nhận 30% &lt;color=Dark&gt;Havoc DMG Bonus&lt;/color&gt;.</t>
+          <t>Resonator nhận 30% &lt;color=Dark&gt;Tăng Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Kỹ Năng Echo, sát thương gây ra của tất cả thành viên trong đội tăng 20%, và Phòng Ngự của họ cũng tăng 20% trong 15 giây, có thể chồng chất tối đa 3 lần.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Echo, DMG gây ra của tất cả thành viên trong đội tăng 20%, và Phòng Ngự của họ cũng tăng 20% trong 15 giây, có thể chồng chất tối đa 3 lần.</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Khi Resonators gây sát thương, họ sẽ hồi phục 10 Concerto Energy. Hiệu ứng này có Cooldown 1,5 giây.</t>
+          <t>Khi Resonator gây sát thương, họ sẽ hồi phục 10 Concerto Energy. Hiệu ứng này có thời gian hồi 1,5 giây.</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Intro Skill, họ hồi phục thêm 40 Resonance Energy. Hiệu ứng này có Cooldown chiêu 10 giây.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Intro, họ hồi phục thêm 40 Resonance Energy. Hiệu ứng này có thời gian hồi chiêu 10 giây.</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Khi HP của Resonators trên 75%, Crit. Rate tăng 20% và Crit. DMG tăng 65%.</t>
+          <t>Khi HP của Resonator trên 75%, Crit. Rate tăng 20% và Crit. DMG tăng 65%.</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Resonators nhận 120% Tăng Sát Thương Kỹ Năng Kết Thúc. Khi Resonators sử dụng Kỹ Năng Kết Thúc, toàn bộ thành viên trong đội được tăng 30% Tấn Công trong 10 giây.</t>
+          <t>Resonator nhận 120% Tăng Sát Thương Outro Skill. Khi Resonator sử dụng Outro Skill, toàn bộ thành viên trong đội được tăng 30% ATK trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Echo Skill DMG Tăng 200%. Khi Resonators sử dụng Kỹ Năng Âm Hưởng, gây thêm 25% sát thương trong 8 giây và phục hồi 30% Resonance Energy.</t>
+          <t>Sát Thương Kỹ Năng Âm Hưởng Tăng 200%. Khi Resonator sử dụng Kỹ Năng Âm Hưởng, gây thêm 25% DMG trong 8 giây và phục hồi 30% Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Khi HP của Resonators trên 75%, Tấn Công tăng 30% và Energy Regen tăng 50%.</t>
+          <t>Khi HP của Resonator trên 75%, ATK tăng 30% và Hồi Năng Lượng tăng 50%.</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Skill, Tấn Công của họ tăng 15% trong 10 giây, có thể chồng chất tối đa 2 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất.</t>
+          <t>Khi Resonator kích hoạt Resonance Skill, ATK của họ tăng 15% trong 10 giây, có thể chồng chất tối đa 2 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất.</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Intro Skill, Tấn Công của họ tăng 5% mỗi giây, có thể chồng chất tối đa 8 lần. Khi đạt tối đa, họ nhận thêm 20% sát thương Resonance Skill Bonus. Hiệu ứng sẽ biến mất khi Resonators rời khỏi chiến trường.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Intro, ATK của họ tăng 5% mỗi giây, có thể chồng chất tối đa 8 lần. Khi đạt tối đa, họ nhận thêm 20% DMG Resonance Skill Bonus. Hiệu ứng sẽ biến mất khi Resonator rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Glacio RES và Spectro của kẻ địch giảm 10%, trong khi kháng Havoc và Aero tăng 10%.</t>
+          <t>Kháng Glacio và Spectro của kẻ địch giảm 10%, trong khi kháng Havoc và Aero tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Havoc RES và Fusion của kẻ địch giảm 10%, trong khi kháng Glacio và Electro tăng 10%.</t>
+          <t>Kháng Havoc và Fusion của kẻ địch giảm 10%, trong khi kháng Glacio và Electro tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Aero RES và kháng Electro của kẻ địch giảm 10%, trong khi kháng Fusion và kháng Spectro tăng 10%.</t>
+          <t>Kháng Aero và kháng Electro của kẻ địch giảm 10%, trong khi kháng Fusion và kháng Spectro tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Tỷ lệ suy giảm Concerto Vibrancy của Kỹ năng Attack Phối Hợp tăng thêm 100%.</t>
+          <t>Tỷ lệ suy giảm Sức Mạnh Rung Động của Kỹ năng Tấn Công Phối Hợp tăng thêm 100%.</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Khi Resonators phản đòn trúng mục tiêu, họ nhận được Tăng Sát Thương Resonance Skill 40% trong 5 giây, có thể tích lũy tối đa 3 lần. Kích hoạt lại hiệu ứng sẽ làm mới thời gian duy trì. Hiệu ứng sẽ mất đi khi Resonators rời khỏi chiến trường.</t>
+          <t>Khi Resonator phản đòn trúng mục tiêu, họ nhận được Tăng Sát Thương Resonance Skill 40% trong 5 giây, có thể tích lũy tối đa 3 lần. Kích hoạt lại hiệu ứng sẽ làm mới thời gian duy trì. Hiệu ứng sẽ mất đi khi Resonator rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Skill, họ nhận thêm 80% thưởng Sát Thương Resonance Liberation trong 5 giây. Khi kích hoạt Resonance Liberation, họ nhận thêm 80% thưởng Sát Thương Resonance Skill trong 5 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian. Hiệu ứng sẽ kết thúc khi Resonators rời khỏi chiến trường.</t>
+          <t>Khi Resonator kích hoạt Resonance Skill, họ nhận thêm 80% thưởng Sát Thương Resonance Liberation trong 5 giây. Khi kích hoạt Resonance Liberation, họ nhận thêm 80% thưởng Sát Thương Resonance Skill trong 5 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian. Hiệu ứng sẽ kết thúc khi Resonator rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Liberation hoặc trúng mục tiêu bằng Dodge Counter, Cooldown chiêu Resonance Skill sẽ giảm 5 giây.</t>
+          <t>Khi Resonator kích hoạt Resonance Liberation hoặc trúng mục tiêu bằng Dodge Counter Tránh, Thời gian hồi chiêu Resonance Skill sẽ giảm 5 giây.</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Skill, họ nhận thêm 80% thưởng Sát Thương Resonance Liberation trong 5 giây. Khi kích hoạt Resonance Liberation, họ nhận thêm 80% thưởng Sát Thương Resonance Skill trong 5 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian. Hiệu ứng sẽ kết thúc khi Resonators rời khỏi chiến trường.</t>
+          <t>Khi Resonator kích hoạt Resonance Skill, họ nhận thêm 80% thưởng Sát Thương Resonance Liberation trong 5 giây. Khi kích hoạt Resonance Liberation, họ nhận thêm 80% thưởng Sát Thương Resonance Skill trong 5 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian. Hiệu ứng sẽ kết thúc khi Resonator rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Liberation hoặc trúng mục tiêu bằng Phản Đòn, Cooldown chiêu Resonance Skill sẽ giảm 5 giây.</t>
+          <t>Khi Resonator kích hoạt Resonance Liberation hoặc trúng mục tiêu bằng Phản Đòn, Thời gian hồi chiêu Resonance Skill sẽ giảm 5 giây.</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation hoặc đánh trúng mục tiêu bằng Dodge Counter sẽ gây hiệu ứng trì trệ trong 3 giây và đánh dấu mục tiêu. Sát thương gây ra lên mục tiêu bị đánh dấu tăng 30%. Dấu hiệu kéo dài 10 giây. Hiệu ứng này có Cooldown chiêu 6 giây.</t>
+          <t>Kích hoạt Resonance Liberation hoặc đánh trúng mục tiêu bằng Dodge Counter Tránh sẽ gây hiệu ứng trì trệ trong 3 giây và đánh dấu mục tiêu. Sát thương gây ra lên mục tiêu bị đánh dấu tăng 30%. Dấu hiệu kéo dài 10 giây. Hiệu ứng này có Thời gian hồi chiêu 6 giây.</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Resonators nhận thêm 30% Sát Thương Resonance Skill. Khi sử dụng Resonance Skill, Tấn Công tăng 15% trong 14 giây.</t>
+          <t>Resonator nhận thêm 30% Sát Thương Resonance Skill. Khi sử dụng Resonance Skill, ATK tăng 15% trong 14 giây.</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Liberation, Tấn Công của họ tăng 5%, và họ nhận thêm 10% thưởng Sát Thương Resonance Skill trong 3 giây, có thể chồng chất tối đa 4 lần. Hiệu ứng sẽ biến mất khi Resonators hiện tại rời khỏi chiến trường.</t>
+          <t>Khi Resonator kích hoạt Resonance Liberation, ATK của họ tăng 5%, và họ nhận thêm 10% thưởng Sát Thương Resonance Skill trong 3 giây, có thể chồng chất tối đa 4 lần. Hiệu ứng sẽ biến mất khi Resonator hiện tại rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu bằng Đòn Phối Hợp sẽ tăng 2% Tấn Công và 4% Sát Thương Resonance Skill cho tất cả thành viên trong đội trong 3 giây, tối đa 10 lần. Mỗi 3 giây sẽ mất 1 lần cộng dồn. Kích hoạt lại sẽ làm mới thời gian hiệu ứng.</t>
+          <t>ATK mục tiêu bằng Đòn Phối Hợp sẽ tăng 2% ATK và 4% Sát Thương Resonance Skill cho tất cả thành viên trong đội trong 3 giây, tối đa 10 lần. Mỗi 3 giây sẽ mất 1 lần cộng dồn. Kích hoạt lại sẽ làm mới thời gian hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Khi HP của Resonators trên 75%, Crit. Rate tăng 15% và Sát Thương Basic Attack tăng 40%.</t>
+          <t>Khi HP của Resonator trên 75%, Crit. Rate tăng 15% và Sát Thương Đòn Cơ Bản tăng 40%.</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng Resonance Liberation sẽ gây 1 lớp &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Mỗi lớp &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; sẽ khiến mục tiêu chịu thêm 5% sát thương.</t>
+          <t>Đánh trúng mục tiêu bằng Resonance Liberation sẽ gây 1 lớp &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Mỗi lớp &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; sẽ khiến mục tiêu chịu thêm 5% DMG.</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Vọng Âm tăng Sát Thương Thuộc Tính cho tất cả Resonators trong đội lên 6%, tối đa 4 lần. Resonators có cùng Vọng Âm không thể kích hoạt hiệu ứng này nhiều lần. Khi đạt 4 điểm, Crit. DMG của tất cả Resonators trong đội tăng thêm 36%.</t>
+          <t>Kích hoạt Kỹ Năng Vọng Âm tăng Sát Thương Thuộc Tính cho tất cả Resonator trong đội lên 6%, tối đa 4 lần. Resonator có cùng Vọng Âm không thể kích hoạt hiệu ứng này nhiều lần. Khi đạt 4 điểm, Crit. DMG của tất cả Resonator trong đội tăng thêm 36%.</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Cộng dồn Sát Thương Heavy Attack tăng thêm 20%. Khi trúng mục tiêu bằng Intro Skill, cộng dồn 2 tầng &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt một lần mỗi giây. Sát thương &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; được khuếch đại thêm 100%.</t>
+          <t>Cộng dồn Sát Thương Đòn Heavy Attack tăng thêm 20%. Khi trúng mục tiêu bằng Kỹ Năng Intro, cộng dồn 2 tầng &lt;color=Highlight&gt;Rối Loạn Spectro&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt một lần mỗi giây. DMG &lt;color=Highlight&gt;Rối Loạn Spectro&lt;/color&gt; được khuếch đại thêm 100%.</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Liberation, Tấn Công của họ tăng 20%, và họ nhận thêm 40% thưởng Spectro DMG trong 12 giây.</t>
+          <t>Khi Resonator kích hoạt Resonance Liberation, ATK của họ tăng 20%, và họ nhận thêm 40% thưởng Sát Thương Spectro trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Tấn Công của Resonators tăng 20%. Khi Resonators gây Aero Erosion lên kẻ địch, Resonators chủ động trong đội nhận thêm 40% Crit. DMG trong 15 giây.</t>
+          <t>ATK của Resonator tăng 20%. Khi Resonator gây Aero Erosion lên kẻ địch, Resonator chủ động trong đội nhận thêm 40% Crit. DMG trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation gây ra một vụ nổ, gây Aero DMG bằng 120% HP tối đa của người sử dụng, kích hoạt mỗi 5 giây một lần. Mục tiêu bị &lt;color=Highlight&gt;Aero Erosion&lt;/color&gt; sẽ bị giảm 30% Phòng Ngự.</t>
+          <t>Kích hoạt Resonance Liberation gây ra một vụ nổ, gây Sát Thương Aero bằng 120% HP tối đa của người sử dụng, kích hoạt mỗi 5 giây một lần. Mục tiêu bị &lt;color=Highlight&gt;Xói Mòn Aero&lt;/color&gt; sẽ bị giảm 30% Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng 25%. Gây sát thương bằng Intro Skill sẽ tạo ra một vụ nổ, gây 1500% Sát Thương Hợp Thể, kích hoạt mỗi 10 giây một lần.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng 25%. Gây DMG bằng Kỹ Năng Khởi Động sẽ tạo ra một vụ nổ, gây 1500% Sát Thương Hợp Thể, kích hoạt mỗi 10 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Intro Skill, Tấn Công của họ tăng 5% mỗi giây, có thể chồng chất tối đa 4 lần. Khi đạt tối đa, họ nhận thêm 40% Fusion DMG Bonus. Hiệu ứng sẽ biến mất khi Resonators rời khỏi chiến trường.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Intro, ATK của họ tăng 5% mỗi giây, có thể chồng chất tối đa 4 lần. Khi đạt tối đa, họ nhận thêm 40% DMG Fusion Bonus. Hiệu ứng sẽ biến mất khi Resonator rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Kỹ Năng Echoes, sát thương gây ra của họ tăng 15%, có thể chồng chất tối đa 2 lần. Cùng một Resonators với Echoes giống nhau không thể kích hoạt hiệu ứng này liên tục. Khi đạt 2 lần chồng chất, mỗi khi gây sát thương, họ sẽ tung ra một đòn tấn công diện rộng gây 800% Havoc DMG, kích hoạt mỗi 10 giây một lần.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Echo, DMG gây ra của họ tăng 15%, có thể chồng chất tối đa 2 lần. Cùng một Resonator với Echo giống nhau không thể kích hoạt hiệu ứng này liên tục. Khi đạt 2 lần chồng chất, mỗi khi gây DMG, họ sẽ tung ra một đòn tấn công diện rộng gây 800% DMG Havoc, kích hoạt mỗi 10 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Sau 60 giây kể từ khi trận chiến bắt đầu, Tổng Sát Thương của Resonators tăng thêm 5%. Sau đó, cứ mỗi 5 giây, Tổng Sát Thương lại tăng thêm 5%, tối đa lên đến 60%.</t>
+          <t>Sau 60 giây kể từ khi trận chiến bắt đầu, Tổng Sát Thương của Resonator tăng thêm 5%. Sau đó, cứ mỗi 5 giây, Tổng Sát Thương lại tăng thêm 5%, tối đa lên đến 60%.</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Intro Skill, họ nhận thêm 30% sát thương Heavy Attack, Electro DMG Bonus và Havoc DMG Bonus trong 30 giây.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Intro, họ nhận thêm 30% DMG Đòn Heavy Attack, DMG Electro Bonus và DMG Havoc Bonus trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Nhận thêm 30% Sát Thương Heavy Attack. Khi kích hoạt Resonance Liberation, Resonators sẽ được bảo vệ bởi một Lớp Shield 3.000 HP, kích hoạt mỗi 4 giây. Resonators được khiên bảo vệ sẽ chịu ít hơn 10% Sát Thương và tăng tổng Sát Thương thêm 16% trong 6 giây, có thể chồng chất lên đến 3 lần. Kích hoạt lại hiệu ứng sẽ làm mới thời gian duy trì.</t>
+          <t>Nhận thêm 30% Sát Thương Heavy Attack. Khi kích hoạt Resonance Liberation, Resonator sẽ được bảo vệ bởi một Lớp Khiên 3.000 HP, kích hoạt mỗi 4 giây. Resonator được khiên bảo vệ sẽ chịu ít hơn 10% Sát Thương và tăng tổng Sát Thương thêm 16% trong 6 giây, có thể chồng chất lên đến 3 lần. Kích hoạt lại hiệu ứng sẽ làm mới thời gian duy trì.</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu ít hơn 10% sát thương. Hiệu ứng này bị bỏ qua khi Resonators có Lớp Khiên.</t>
+          <t>Kẻ địch chịu ít hơn 10% DMG. Hiệu ứng này bị bỏ qua khi Resonator có Lớp Khiên.</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Liberation, họ sẽ nhận được Shield trị giá 3000 điểm. Khi nhận Shield, Sát Thương Thuộc Tính của họ tăng 10%, và Tấn Công tăng 12% trong 10 giây, có thể chồng chất tối đa 3 lần. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.</t>
+          <t>Khi Resonator kích hoạt Resonance Liberation, họ sẽ nhận được Khiên trị giá 3000 điểm. Khi nhận Khiên, Sát Thương Thuộc Tính của họ tăng 10%, và ATK tăng 12% trong 10 giây, có thể chồng chất tối đa 3 lần. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng 35%, và Sát Thương Kỹ Năng Hồi Âm được Khuếch Đại thêm 50%. Khi Resonators sử dụng Intro Skill, họ sẽ nhận thêm 50% Tăng Sát Thương Heavy Attack trong 30 giây.</t>
+          <t>Crit. DMG tăng 35%, và Sát Thương Kỹ Năng Hồi Âm được Khuếch Đại thêm 50%. Khi Resonator sử dụng Kỹ Năng Khởi Động, họ sẽ nhận thêm 50% Tăng Sát Thương Đòn Nặng trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Echo Skill DMG Được Khuếch Đại 20%. Khi Resonators sử dụng Intro Skill, nhận thêm 30% Tấn Công Nặng trong 30 giây.</t>
+          <t>Sát Thương Kỹ Năng Âm Hưởng Được Khuếch Đại 20%. Khi Resonator sử dụng Kỹ Năng Khởi Động, nhận thêm 30% ATK Nặng trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Sát thương nhận vào (trừ sát thương Status Tiêu Cực) của kẻ địch giảm 10%. Hiệu ứng này không hoạt động với kẻ địch đang mang Status Tiêu Cực.</t>
+          <t>DMG nhận vào (trừ DMG Trạng Thái Tiêu Cực) của kẻ địch giảm 10%. Hiệu ứng này không hoạt động với kẻ địch đang mang Trạng Thái Tiêu Cực.</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Resonators bỏ qua 30% Phòng Ngự của kẻ địch khi gây sát thương. Sát Thương Status Tiêu Cực do Resonators trong đội gây ra tăng 30%. Khi kẻ địch bị Nguyền Rủa Havoc, sát thương nhận vào sẽ tăng 30%.</t>
+          <t>Resonator bỏ qua 30% Phòng Ngự của kẻ địch khi gây DMG. Sát Thương Trạng Thái Tiêu Cực do Resonator trong đội gây ra tăng 30%. Khi kẻ địch bị Nguyền Rủa Havoc, DMG nhận vào sẽ tăng 30%.</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng 20%. Gây sát thương bằng Basic Attack sẽ nhận thêm 5% Tăng Sát Thương Toàn Thuộc Tính trong 6 giây, tối đa 8 lần cộng dồn. Kích hoạt lại hiệu ứng sẽ làm mới thời gian, và hiệu ứng sẽ biến mất khi Resonator rời khỏi chiến trường.</t>
+          <t>Crit. DMG tăng 20%. Gây DMG bằng Đòn Cơ Bản sẽ nhận thêm 5% Tăng Sát Thương Toàn Thuộc Tính trong 6 giây, tối đa 8 lần cộng dồn. Kích hoạt lại hiệu ứng sẽ làm mới thời gian, và hiệu ứng sẽ biến mất khi Resonator rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu thêm 40% Sát Thương Resonance Liberation. Tỷ lệ deplete Vibration Strength của kẻ địch tăng thêm 50%. Khi bị Status Tiêu Cực, tỷ lệ deplete Vibration Strength của chúng tăng thêm 50%. Khi Resonators tấn công kẻ địch Bất Động, tổng Sát Thương của họ tăng thêm 50% trong 20 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.</t>
+          <t>Kẻ địch chịu thêm 40% Sát Thương Resonance Liberation. Tỷ lệ Giảm Sức Rung của kẻ địch tăng thêm 50%. Khi bị Trạng Thái Tiêu Cực, tỷ lệ Giảm Sức Rung của chúng tăng thêm 50%. Khi Resonator tấn công kẻ địch Bất Động, tổng Sát Thương của họ tăng thêm 50% trong 20 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       <c r="M140" t="inlineStr">
         <is>
           <t>Kẻ địch bắt đầu với 5 lớp Kháng toàn thuộc tính, mỗi lớp tăng 8%.
-Sử dụng Kỹ Năng Echoes sẽ giúp Resonators trong đội bỏ qua 1 lớp Kháng toàn thuộc tính. Resonators không thể kích hoạt hiệu ứng này liên tục bằng các Echoes cùng tên.</t>
+Sử dụng Kỹ Năng Echo sẽ giúp Resonator trong đội bỏ qua 1 lớp Kháng toàn thuộc tính. Resonator không thể kích hoạt hiệu ứng này liên tục bằng các Echo cùng tên.</t>
         </is>
       </c>
     </row>
@@ -9633,9 +9633,9 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu Sát Thương Echoes tăng 40%, và Sát Thương Status Tiêu Cực được khuếch đại thêm 60%.
-Sử dụng kỹ năng Echoes sẽ giúp Resonators trong đội nhận 1 tầng Crest Enhancement, tối đa 5 tầng. Resonators không thể kích hoạt hiệu ứng này nhiều lần với Echoes cùng tên.
-Ở tầng 1/2/3/4/5, tổng sát thương gây ra tăng lần lượt 15%/20%/25%/30%/40%.</t>
+          <t>Kẻ địch chịu Sát Thương Echo tăng 40%, và Sát Thương Trạng Thái Tiêu Cực được khuếch đại thêm 60%.
+Sử dụng kỹ năng Echo sẽ giúp Resonator trong đội nhận 1 tầng Crest Enhancement, tối đa 5 tầng. Resonator không thể kích hoạt hiệu ứng này nhiều lần với Echo cùng tên.
+Ở tầng 1/2/3/4/5, tổng DMG gây ra tăng lần lượt 15%/20%/25%/30%/40%.</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Kháng toàn bộ thuộc tính của kẻ địch tăng 15%. Hiệu ứng này không ảnh hưởng đến Resonators đang có khiên. Khi kẻ địch chịu Sát Thương Vỡ Nhạc, hiệu ứng này sẽ bị loại bỏ.</t>
+          <t>Kháng toàn bộ thuộc tính của kẻ địch tăng 15%. Hiệu ứng này không ảnh hưởng đến Resonator đang có khiên. Khi kẻ địch chịu Sát Thương Vỡ Nhạc, hiệu ứng này sẽ bị loại bỏ.</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Nhận thêm 30% Sát Thương Basic Attack. Khi Resonators tấn công kẻ địch bị Trạng Thái Điều Tiết - Dao Động hoặc Trạng Thái Điều Tiết - Giao Thoa, họ nhận thêm 50% Spectro DMG.</t>
+          <t>Nhận thêm 30% Sát Thương Basic Attack. Khi Resonator tấn công kẻ địch bị Trạng Thái Điều Tiết - Dao Động hoặc Trạng Thái Điều Tiết - Giao Thoa, họ nhận thêm 50% Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu ảnh hưởng bởi Fusion Burst nhận thêm 100% tổng sát thương. Khi kẻ địch ở trạng thái Tune Strain - Interfered, chúng chịu thêm 50% tổng sát thương từ Basic Attack. Khi Resonators sử dụng Intro Skill, họ gây thêm 25% tổng sát thương, và Hệ Số Sát Thương Tune Rupture của tất cả Resonators trong đội tăng 100%. Hiệu ứng này kéo dài trong 15 giây.</t>
+          <t>Kẻ địch chịu ảnh hưởng bởi Fusion Burst nhận thêm 100% tổng DMG. Khi kẻ địch ở trạng thái Tune Strain - Interfered, chúng chịu thêm 50% tổng DMG từ ATK Cơ Bản. Khi Resonator sử dụng Kỹ Năng Khởi Động, họ gây thêm 25% tổng DMG, và Hệ Số Sát Thương Tune Rupture của tất cả Resonator trong đội tăng 100%. Hiệu ứng này kéo dài trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng 20%. Khi Resonators sử dụng Intro Skill, họ sẽ nhận thêm 30% Tăng Sát Thương Resonance Liberation và Tăng Sát Thương Heavy Attack trong 15 giây.</t>
+          <t>Crit. DMG tăng 20%. Khi Resonator sử dụng Kỹ Năng Khởi Động, họ sẽ nhận thêm 30% Tăng Sát Thương Resonance Liberation và Tăng Sát Thương Đòn Nặng trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Kháng toàn thuộc tính của kẻ địch tăng 15%. Hiệu ứng này sẽ bị loại bỏ khi chúng chịu Sát Thương Vỡ Tune hoặc Fusion DMG Burst, hoặc khi bị tấn công trong trạng thái Tune Strain - Interfered.</t>
+          <t>Kháng toàn thuộc tính của kẻ địch tăng 15%. Hiệu ứng này sẽ bị loại bỏ khi chúng chịu Sát Thương Vỡ Tune hoặc Sát Thương Fusion Burst, hoặc khi bị tấn công trong trạng thái Tune Strain - Interfered.</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10025,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng 30%. Kẻ địch chịu thêm 150% sát thương tổng từ Kỹ Năng Bùng Nổ Tổng Hợp. Khi Resonators tấn công kẻ địch dưới trạng thái Nhiễu Loạn Giai Tune - Biến Đổi hoặc Nhiễu Loạn Giai Tune - Giao Thoa, họ sẽ nhận thêm 50% Spectro DMG Bonus.</t>
+          <t>Crit. DMG tăng 30%. Kẻ địch chịu thêm 150% DMG tổng từ Kỹ Năng Bùng Nổ Tổng Hợp. Khi Resonator tấn công kẻ địch dưới trạng thái Nhiễu Loạn Giai Điệu - Biến Đổi hoặc Nhiễu Loạn Giai Điệu - Giao Thoa, họ sẽ nhận thêm 50% Tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Resonators gây thêm 20% tổng Aero DMG và 30% tổng sát thương Kỹ Năng Echo. Khi Resonators sử dụng Intro Skill, tổng sát thương của họ sẽ tăng 20% trong 20 giây.</t>
+          <t>Resonator gây thêm 20% tổng DMG Aero và 30% tổng DMG Kỹ Năng Echo. Khi Resonator sử dụng Kỹ Năng Khởi Động, tổng DMG của họ sẽ tăng 20% trong 20 giây.</t>
         </is>
       </c>
     </row>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng 25%. Khi Resonators sử dụng Intro Skill, họ sẽ nhận thêm 40% Tăng Sát Thương Heavy Attack và Tăng Sát Thương Resonance Liberation trong 20 giây.</t>
+          <t>Crit. DMG tăng 25%. Khi Resonator sử dụng Kỹ Năng Khởi Động, họ sẽ nhận thêm 40% Tăng Sát Thương Đòn Nặng và Tăng Sát Thương Resonance Liberation trong 20 giây.</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Kháng toàn thuộc tính của kẻ địch tăng 15%. Hiệu ứng này sẽ bị loại bỏ khi chúng chịu Sát Thương Vỡ Tune hoặc Glacio DMG Chafe, hoặc khi nhận sát thương trong trạng thái Tune Strain - Interfered.</t>
+          <t>Kháng toàn thuộc tính của kẻ địch tăng 15%. Hiệu ứng này sẽ bị loại bỏ khi chúng chịu Sát Thương Vỡ Tune hoặc Sát Thương Glacio Chafe, hoặc khi nhận DMG trong trạng thái Tune Strain - Interfered.</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Total Sát Thương tăng 20%. Khi Resonators trong đội gây trạng thái Tunability - Shifting, tổng Sát Thương gây ra của họ tăng thêm 20% trong 15 giây. Kẻ địch chịu thêm 30% tổng Glacio DMG, 40% tổng Sát Thương Kỹ Năng Echo và 100% tổng Glacio DMG Chafe.</t>
+          <t>Tổng Sát Thương tăng 20%. Khi Resonator trong đội gây trạng thái Tunability - Shifting, tổng Sát Thương gây ra của họ tăng thêm 20% trong 15 giây. Kẻ địch chịu thêm 30% tổng Sát Thương Glacio, 40% tổng Sát Thương Kỹ Năng Echo và 100% tổng Sát Thương Glacio Chafe.</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Tấn Công tăng 20%. Resonators nhận 30% Tăng Sát Thương Toàn Bộ trong 20 giây khi sử dụng Intro Skill.</t>
+          <t>ATK tăng 20%. Resonator nhận 30% Tăng Sát Thương Toàn Bộ trong 20 giây khi sử dụng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Kháng toàn thuộc tính của kẻ địch tăng 15%. Hiệu ứng này sẽ bị loại bỏ khi chúng chịu Sát Thương Status Tiêu Cực hoặc bị ảnh hưởng bởi Tune Strain - Shifting.</t>
+          <t>Kháng toàn thuộc tính của kẻ địch tăng 15%. Hiệu ứng này sẽ bị loại bỏ khi chúng chịu Sát Thương Trạng Thái Tiêu Cực hoặc bị ảnh hưởng bởi Tune Strain - Shifting.</t>
         </is>
       </c>
     </row>
@@ -10481,8 +10481,8 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Tấn Công tăng 30%, Total Glacio DMG tăng 30%.
-Kẻ địch chịu thêm 80% Total Sát Thương Chafe Glacio và 160% Total Fusion DMG Burst. Sau khi Resonator gây Tune Strain - Shifting, tổng sát thương kẻ địch phải chịu tăng 50% trong 20 giây.</t>
+          <t>ATK tăng 30%, Tổng Sát Thương Glacio tăng 30%.
+Kẻ địch chịu thêm 80% Tổng Sát Thương Chafe Glacio và 160% Tổng Sát Thương Fusion Burst. Sau khi Resonator gây Tune Strain - Shifting, tổng DMG kẻ địch phải chịu tăng 50% trong 20 giây.</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Sau 60 giây kể từ khi trận chiến bắt đầu, mỗi khi Resonator tấn công trúng kẻ địch, kẻ địch đó sẽ chịu thêm 5% Total Sát Thương trong 15 giây. Giá trị này tăng thêm 5% sau mỗi 5 giây, tối đa lên đến 60%.</t>
+          <t>Sau 60 giây kể từ khi trận chiến bắt đầu, mỗi khi Resonator tấn công trúng kẻ địch, kẻ địch đó sẽ chịu thêm 5% Tổng Sát Thương trong 15 giây. Giá trị này tăng thêm 5% sau mỗi 5 giây, tối đa lên đến 60%.</t>
         </is>
       </c>
     </row>
@@ -10613,8 +10613,8 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;KU-Money's Shop&lt;/te&gt;]&lt;/color&gt;
-Mỗi lần mua vật phẩm hoặc Chiến Thuật tại Shop KU-Money, Tấn Công của Combat Machines sẽ tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Cửa Hàng KU-Money&lt;/te&gt;]&lt;/color&gt;
+Mỗi lần mua vật phẩm hoặc Chiến Thuật tại Cửa Hàng KU-Money, ATK của Máy Chiến Đấu sẽ tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10680,8 +10680,8 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Tấn Công của Combat Machines tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;. Cứ mỗi 5 đợt, Tấn Công của chúng lại tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; nữa.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+ATK của Máy Chiến Đấu tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;. Cứ mỗi 5 đợt, ATK của chúng lại tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; nữa.</t>
         </is>
       </c>
     </row>
@@ -10747,8 +10747,8 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Khi một Discord chạm đến Energy Matrix, nó gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương cố định lên tất cả Discord trên chiến trường.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Khi một Tacet Discord chạm đến Ma Trận Năng Lượng, nó gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương cố định lên tất cả Tacet Discord trên chiến trường.</t>
         </is>
       </c>
     </row>
@@ -10814,8 +10814,8 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Khi Độ Bền của Energy Matrix còn &lt;color=Highlight&gt;{0}&lt;/color&gt;, Tấn Công của Combat Machines tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Khi Độ Bền của Ma Trận Năng Lượng còn &lt;color=Highlight&gt;{0}&lt;/color&gt;, ATK của Máy Chiến Đấu tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10881,8 +10881,8 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss bạn sở hữu, Tấn Công của Combat Machines tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits bạn sở hữu, ATK của Máy Chiến Đấu tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10948,8 +10948,8 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss bạn sở hữu, Tấn Công của Combat Machines tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits bạn sở hữu, ATK của Máy Chiến Đấu tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11015,8 +11015,8 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss bạn sở hữu, Crit. Rate của Combat Machines tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits bạn sở hữu, Crit. Rate của Máy Chiến Đấu tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11082,8 +11082,8 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss bạn sở hữu, Crit. Rate của Combat Machines tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits bạn sở hữu, Crit. Rate của Máy Chiến Đấu tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11149,8 +11149,8 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss bạn sở hữu, Crit. DMG của Combat Machines tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits bạn sở hữu, Crit. DMG của Máy Chiến Đấu tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11216,8 +11216,8 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss bạn sở hữu, Crit. Rate của Combat Machines tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits bạn sở hữu, Crit. Rate của Máy Chiến Đấu tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, tối đa bằng số đợt * &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11283,8 +11283,8 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750029&gt;Silver Bullet&lt;/te&gt;]&lt;/color&gt;
-Triển khai Combat Machines tốn ít hơn &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss. Triển khai một Combat Machines sẽ tăng Tấn Công cho các Combat Machines trong &lt;color=Highlight&gt;{1}&lt;/color&gt; ô lưới lân cận thêm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750029&gt;Viên Đạn Bạc&lt;/te&gt;]&lt;/color&gt;
+Triển khai Máy Chiến Đấu tốn ít hơn &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits. Triển khai một Máy Chiến Đấu sẽ tăng ATK cho các Máy Chiến Đấu trong &lt;color=Highlight&gt;{1}&lt;/color&gt; ô lưới lân cận thêm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11350,8 +11350,8 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750029&gt;Silver Bullet&lt;/te&gt;]&lt;/color&gt;
-Triển khai Combat Machines tốn ít hơn &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss. Triển khai một Combat Machines sẽ tăng Tấn Công cho các Combat Machines trong &lt;color=Highlight&gt;{1}&lt;/color&gt; ô lưới lân cận thêm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750029&gt;Viên Đạn Bạc&lt;/te&gt;]&lt;/color&gt;
+Triển khai Máy Chiến Đấu tốn ít hơn &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits. Triển khai một Máy Chiến Đấu sẽ tăng ATK cho các Máy Chiến Đấu trong &lt;color=Highlight&gt;{1}&lt;/color&gt; ô lưới lân cận thêm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11417,8 +11417,8 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Tiêu diệt Tacet Discord sẽ rơi thêm Lucky Coin. Tất cả Combat Machines có Crit. Rate tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Tiêu diệt Tacet Discord sẽ rơi thêm Đồng Xu May Mắn. Tất cả Máy Chiến Đấu có Crit. Rate tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11484,8 +11484,8 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Tiêu diệt Tacet Discord sẽ rơi thêm Lucky Coin. Tất cả Combat Machines có Crit. Rate tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Tiêu diệt Tacet Discord sẽ rơi thêm Đồng Xu May Mắn. Tất cả Máy Chiến Đấu có Crit. Rate tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11551,8 +11551,8 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Lucky Coin sẽ tự động được thu thập sau &lt;color=Highlight&gt;{0}&lt;/color&gt; giây kể từ khi rơi. Tất cả Combat Machines có Tấn Công tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Đồng Xu May Mắn sẽ tự động được thu thập sau &lt;color=Highlight&gt;{0}&lt;/color&gt; giây kể từ khi rơi. Tất cả Máy Chiến Đấu có ATK tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11618,8 +11618,8 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Lucky Coin sẽ tự động được thu thập sau &lt;color=Highlight&gt;{0}&lt;/color&gt; giây kể từ khi rơi. Tất cả Combat Machines có Tấn Công tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Đồng Xu May Mắn sẽ tự động được thu thập sau &lt;color=Highlight&gt;{0}&lt;/color&gt; giây kể từ khi rơi. Tất cả Máy Chiến Đấu có ATK tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11686,9 +11686,9 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750023&gt;Fusion-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Khi Combat Machines Loại Fusion gây sát thương, có &lt;color=Highlight&gt;{0}&lt;/color&gt; xác suất tiêu diệt trực tiếp Tacet Discord nhỏ (thay vào đó gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Fusion DMG lên Tacet Discord cỡ trung).
-Tacet Discord bị tiêu diệt bởi Combat Machines Loại Fusion có &lt;color=Highlight&gt;{2}&lt;/color&gt; xác suất rơi 1 đống Lucky Coin. Khi Hologram Echo: Chest Mimic kích hoạt hiệu ứng này, số lượng Lucky Coin rơi sẽ tăng gấp đôi.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750023&gt;Máy Chiến Đấu Loại Fusion&lt;/te&gt;]&lt;/color&gt;
+Khi Máy Chiến Đấu Loại Fusion gây DMG, có &lt;color=Highlight&gt;{0}&lt;/color&gt; xác suất tiêu diệt trực tiếp Tacet Discord nhỏ (thay vào đó gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương Fusion lên Tacet Discord cỡ trung).
+Tacet Discord bị tiêu diệt bởi Máy Chiến Đấu Loại Fusion có &lt;color=Highlight&gt;{2}&lt;/color&gt; xác suất rơi 1 đống Đồng Xu May Mắn. Khi Hologram Echo: Chest Mimic kích hoạt hiệu ứng này, số lượng Đồng Xu May Mắn rơi sẽ tăng gấp đôi.</t>
         </is>
       </c>
     </row>
@@ -11755,9 +11755,9 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750023&gt;Fusion-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Khi Combat Machines Loại Fusion gây sát thương, có &lt;color=Highlight&gt;{0}&lt;/color&gt; xác suất tiêu diệt trực tiếp Tacet Discord nhỏ (thay vào đó gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Fusion DMG lên Tacet Discord cỡ trung).
-Tacet Discord bị tiêu diệt bởi Combat Machines Loại Fusion có &lt;color=Highlight&gt;{2}&lt;/color&gt; xác suất rơi 1 đống Lucky Coin. Khi Hologram Echo: Chest Mimic kích hoạt hiệu ứng này, số lượng Lucky Coin rơi sẽ tăng gấp đôi.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750023&gt;Máy Chiến Đấu Loại Fusion&lt;/te&gt;]&lt;/color&gt;
+Khi Máy Chiến Đấu Loại Fusion gây DMG, có &lt;color=Highlight&gt;{0}&lt;/color&gt; xác suất tiêu diệt trực tiếp Tacet Discord nhỏ (thay vào đó gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương Fusion lên Tacet Discord cỡ trung).
+Tacet Discord bị tiêu diệt bởi Máy Chiến Đấu Loại Fusion có &lt;color=Highlight&gt;{2}&lt;/color&gt; xác suất rơi 1 đống Đồng Xu May Mắn. Khi Hologram Echo: Chest Mimic kích hoạt hiệu ứng này, số lượng Đồng Xu May Mắn rơi sẽ tăng gấp đôi.</t>
         </is>
       </c>
     </row>
@@ -11823,8 +11823,8 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; có Tấn Công tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; có ATK tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11890,8 +11890,8 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; có Tấn Công tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; có ATK tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11957,8 +11957,8 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; có Crit. Rate tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; có Crit. Rate tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12024,8 +12024,8 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; có Crit. Rate tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; có Crit. Rate tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12091,8 +12091,8 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; có Crit. DMG tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; có Crit. DMG tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12158,8 +12158,8 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; có Crit. DMG tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; có Crit. DMG tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12225,8 +12225,8 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Combat Machines trên trần tăng Crit. DMG thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu trên trần tăng Crit. DMG thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12292,8 +12292,8 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Combat Machines trên trần tăng Crit. DMG thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu trên trần tăng Crit. DMG thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12359,8 +12359,8 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Enhancement Field&lt;/te&gt;]&lt;/color&gt;
-Mỗi Máy Combat Kiểu Fusion xung quanh Máy Combat &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; sẽ tăng Tấn Công của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
+Mỗi Máy Chiến Đấu Kiểu Fusion xung quanh Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; sẽ tăng ATK của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -12426,8 +12426,8 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Enhancement Field&lt;/te&gt;]&lt;/color&gt;
-Mỗi Máy Combat Kiểu Fusion xung quanh Máy Combat &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; sẽ tăng Tấn Công của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
+Mỗi Máy Chiến Đấu Kiểu Fusion xung quanh Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; sẽ tăng ATK của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -12493,8 +12493,8 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Enhancement Field&lt;/te&gt;]&lt;/color&gt;
-Mỗi Máy Combat Kiểu Electro xung quanh Máy Combat &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; sẽ tăng Crit. Rate của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
+Mỗi Máy Chiến Đấu Kiểu Electro xung quanh Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; sẽ tăng Crit. Rate của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -12560,8 +12560,8 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Enhancement Field&lt;/te&gt;]&lt;/color&gt;
-Mỗi Máy Combat Kiểu Electro xung quanh Máy Combat &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; sẽ tăng Crit. Rate của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
+Mỗi Máy Chiến Đấu Kiểu Electro xung quanh Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; sẽ tăng Crit. Rate của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -12627,8 +12627,8 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Enhancement Field&lt;/te&gt;]&lt;/color&gt;
-Mỗi Máy Combat Kiểu Glacio xung quanh Máy Combat &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; sẽ tăng Crit. DMG của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
+Mỗi Máy Chiến Đấu Kiểu Glacio xung quanh Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; sẽ tăng Crit. DMG của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -12694,8 +12694,8 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Enhancement Field&lt;/te&gt;]&lt;/color&gt;
-Mỗi Máy Combat Kiểu Electro xung quanh Máy Combat &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; sẽ tăng Crit. DMG của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
+Mỗi Máy Chiến Đấu Kiểu Electro xung quanh Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; sẽ tăng Crit. DMG của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -12763,10 +12763,10 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Mỗi khi Hologram Echo: Chest Mimic tấn công 5 lần hoặc cứ sở hữu &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss, Tấn Công của nó sẽ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{2}&lt;/color&gt; giây.
-Khi đánh bại Tacet Discord, Hologram Echo: Chest Mimic có &lt;color=Highlight&gt;{3}&lt;/color&gt;% cơ hội rơi ra &lt;color=Highlight&gt;{4}&lt;/color&gt; Lucky Coin.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Mỗi khi Hologram Echo: Chest Mimic tấn công 5 lần hoặc cứ sở hữu &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits, ATK của nó sẽ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{2}&lt;/color&gt; giây.
+Khi đánh bại Tacet Discord, Hologram Echo: Chest Mimic có &lt;color=Highlight&gt;{3}&lt;/color&gt;% cơ hội rơi ra &lt;color=Highlight&gt;{4}&lt;/color&gt; Đồng Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -12834,10 +12834,10 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Mỗi khi Hologram Echo: Chest Mimic tấn công 5 lần hoặc cứ sở hữu &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss, Tấn Công của nó sẽ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{2}&lt;/color&gt; giây.
-Khi đánh bại Tacet Discord, Hologram Echo: Chest Mimic có &lt;color=Highlight&gt;{3}&lt;/color&gt;% cơ hội rơi ra &lt;color=Highlight&gt;{4}&lt;/color&gt; Lucky Coin.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Mỗi khi Hologram Echo: Chest Mimic tấn công 5 lần hoặc cứ sở hữu &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits, ATK của nó sẽ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{2}&lt;/color&gt; giây.
+Khi đánh bại Tacet Discord, Hologram Echo: Chest Mimic có &lt;color=Highlight&gt;{3}&lt;/color&gt;% cơ hội rơi ra &lt;color=Highlight&gt;{4}&lt;/color&gt; Đồng Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
 Tacet Discord bị trúng Hologram Echo: Junrock sẽ bị giảm toàn bộ Kháng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; trong &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
         </is>
       </c>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
 Tacet Discord bị trúng Hologram Echo: Junrock sẽ bị giảm toàn bộ Kháng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; trong &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
         </is>
       </c>
@@ -13037,8 +13037,8 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Khi bị trúng Hologram Echo: Puff, Tacet Discord sẽ chịu thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; sát thương từ các Combat Machines &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; trong &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+Khi bị trúng Hologram Echo: Puff, Tacet Discord sẽ chịu thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; DMG từ các Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; trong &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
         </is>
       </c>
     </row>
@@ -13104,8 +13104,8 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Khi bị trúng Hologram Echo: Puff, Tacet Discord sẽ chịu thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; sát thương từ các Combat Machines &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; trong &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+Khi bị trúng Hologram Echo: Puff, Tacet Discord sẽ chịu thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; DMG từ các Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; trong &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
         </is>
       </c>
     </row>
@@ -13171,8 +13171,8 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Khi Hologram Echo: Hoartoise đang trong Cooldown chiêu, các Combat Machines &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; trong phạm vi &lt;color=Highlight&gt;{0}&lt;/color&gt; ô lưới xung quanh sẽ có Attack Speed tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; và Attack tăng &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+Khi Hologram Echo: Hoartoise đang trong Thời gian hồi chiêu, các Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; trong phạm vi &lt;color=Highlight&gt;{0}&lt;/color&gt; ô lưới xung quanh sẽ có Tốc Độ ATK tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; và ATK tăng &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13238,8 +13238,8 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Echo-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Khi Hologram Echo: Hoartoise đang trong Cooldown chiêu, các Combat Machines &lt;color=Highlight&gt;Echo-Type&lt;/color&gt; trong phạm vi &lt;color=Highlight&gt;{0}&lt;/color&gt; ô lưới xung quanh sẽ có Attack Speed tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; và Attack tăng &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750021&gt;Máy Chiến Đấu Kiểu Echo&lt;/te&gt;]&lt;/color&gt;
+Khi Hologram Echo: Hoartoise đang trong Thời gian hồi chiêu, các Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; trong phạm vi &lt;color=Highlight&gt;{0}&lt;/color&gt; ô lưới xung quanh sẽ có Tốc Độ ATK tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; và ATK tăng &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13304,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Tăng cường Electro (Tỉ lệ Crit.)</t>
+          <t>Tăng Cường Electro (Crit. Rate)</t>
         </is>
       </c>
     </row>
@@ -13369,7 +13369,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Tăng cường Electro (Tỉ lệ Crit.)</t>
+          <t>Tăng Cường Electro (Crit. Rate)</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Tăng cường Glacio (Tỉ lệ Crit.)</t>
+          <t>Tăng Cường Glacio (Crit. Rate)</t>
         </is>
       </c>
     </row>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Tăng cường Glacio (Tỉ lệ Crit.)</t>
+          <t>Tăng Cường Glacio (Crit. Rate)</t>
         </is>
       </c>
     </row>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Tăng cường Shell Credit (ATK)</t>
+          <t>Tăng Shell Credit (ATK)</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Tăng cường Shell Credit (ATK)</t>
+          <t>Tăng Shell Credit (ATK)</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Tăng cường Shell Credit (Tỉ lệ Crit.)</t>
+          <t>Tăng Shell Credit (Crit. Rate)</t>
         </is>
       </c>
     </row>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Tăng cường Shell Credit (Tỉ lệ Crit.)</t>
+          <t>Tăng Shell Credit (Crit. Rate)</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Tăng cường Shell Credit (DMG Crit.)</t>
+          <t>Tăng Shell Credit (Crit. DMG)</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Tăng cường Shell Credit (DMG Crit.)</t>
+          <t>Tăng Shell Credit (Crit. DMG)</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Tăng cường Echo (ATK)</t>
+          <t>Tăng Cường Echo (ATK)</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Tăng cường Echo (ATK)</t>
+          <t>Tăng Cường Echo (ATK)</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Tăng cường Echo (Tỉ lệ Crit.)</t>
+          <t>Tăng Cường Echo (Crit. Rate)</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Tăng cường Echo (Tỉ lệ Crit.)</t>
+          <t>Tăng Cường Echo (Crit. Rate)</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Tăng cường Echo (DMG Crit.)</t>
+          <t>Tăng Cường Echo (Crit. DMG)</t>
         </is>
       </c>
     </row>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Tăng cường Echo (DMG Crit.)</t>
+          <t>Tăng Cường Echo (Crit. DMG)</t>
         </is>
       </c>
     </row>
@@ -14344,7 +14344,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Kỹ Năng Thường</t>
+          <t>Kỹ năng thông thường</t>
         </is>
       </c>
     </row>
@@ -14539,7 +14539,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Skill Echo đang kích hoạt. Không thể thực hiện hành động này.</t>
+          <t>Kỹ năng Echo đang kích hoạt. Không thể thực hiện hành động này.</t>
         </is>
       </c>
     </row>
@@ -14604,7 +14604,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đặc Biệt</t>
+          <t>Kỹ Năng Độc Quyền</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
 Một Tacet Discord hình người chưa trưởng thành. Trên cơ thể nó còn vương lại những tinh thể băng nhỏ. Nó dùng chúng để bắt chước âm thanh "leng keng" của băng va chạm.</t>
         </is>
       </c>
@@ -14736,7 +14736,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Skill Training Combat Basic</t>
+          <t>Huấn Luyện Kỹ Năng Chiến Đấu Cơ Bản</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Tôi là Xiangli Yao, nhà nghiên cứu tại Huaxu Academy. Rover à, những tần số cộng hưởng hiếm có của ngươi đặt ra một câu hỏi thú vị: liệu ngươi là ngọn hải đăng độc nhất soi sáng con đường tìm kiếm chân lý của chúng ta? Hay ngươi đã nắm giữ chân lý tối thượng trong tay?</t>
+          <t>Tôi là Xiangli Yao, nhà nghiên cứu tại Học viện Huaxu. Vận Mệnh Giả à, những tần số cộng hưởng hiếm có của ngươi đặt ra một câu hỏi thú vị: liệu ngươi là ngọn hải đăng độc nhất soi sáng con đường tìm kiếm chân lý của chúng ta? Hay ngươi đã nắm giữ chân lý tối thượng trong tay?</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Kuchiba Chisa. Chương trình Phát triển Chiến thuật, Khoa Kỹ thuật, Startorch Academy. Chuyên ngành Forte: phân tích cấu trúc... Xin lỗi, có lẽ giờ không phải lúc để nói chuyện kiểu cách thế này.</t>
+          <t>Kuchiba Chisa. Chương trình Phát triển Chiến thuật, Khoa Kỹ thuật, Học viện Startorch. Chuyên ngành Forte: phân tích cấu trúc... Xin lỗi, có lẽ giờ không phải lúc để nói chuyện kiểu cách thế này.</t>
         </is>
       </c>
     </row>
@@ -14931,7 +14931,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Khi có mục tiêu tấn công trong tầm, nó sẽ bị khóa. Nhấn nút này để Switch mục tiêu khác.</t>
+          <t>Khi có mục tiêu tấn công trong tầm, nó sẽ bị khóa. Nhấn nút này để Chuyển mục tiêu khác.</t>
         </is>
       </c>
     </row>
@@ -14996,7 +14996,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Khi có mục tiêu tấn công trong tầm, nó sẽ bị khóa. Nhấn nút này để Switch mục tiêu khác.</t>
+          <t>Khi có mục tiêu tấn công trong tầm, nó sẽ bị khóa. Nhấn nút này để Chuyển mục tiêu khác.</t>
         </is>
       </c>
     </row>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Sát thương ngoài phạm vi của Resonators tăng 100%.</t>
+          <t>DMG ngoài phạm vi của Resonator tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Liberation, Tấn Công của họ tăng 8% và Kháng Sát Thương tăng 5% mỗi giây, có thể chồng chất tối đa 6 lần và kéo dài trong 14 giây. Hiệu ứng sẽ kết thúc khi Resonators rời khỏi chiến trường.</t>
+          <t>Khi Resonator kích hoạt Resonance Liberation, ATK của họ tăng 8% và Kháng Sát Thương tăng 5% mỗi giây, có thể chồng chất tối đa 6 lần và kéo dài trong 14 giây. Hiệu ứng sẽ kết thúc khi Resonator rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Intro Skill, họ nhận được một Lá Chắn kéo dài 8 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian. Khi nhận bất kỳ loại Lá Chắn nào, Tấn Công của Resonators tăng 20% và Crit. DMG tăng 30% trong 12 giây.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Intro, họ nhận được một Lá Chắn kéo dài 8 giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian. Khi nhận bất kỳ loại Lá Chắn nào, ATK của Resonator tăng 20% và Crit. DMG tăng 30% trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Skill, Tấn Công của họ tăng 20% trong 7 giây, có thể chồng chất tối đa 2 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất.</t>
+          <t>Khi Resonator kích hoạt Resonance Skill, ATK của họ tăng 20% trong 7 giây, có thể chồng chất tối đa 2 lần. Thời gian hiệu ứng sẽ được làm mới với mỗi lần chồng chất.</t>
         </is>
       </c>
     </row>
@@ -15386,7 +15386,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Wind&gt;Aero RES&lt;/color&gt; và &lt;color=Light&gt;Spectro RES&lt;/color&gt; của kẻ địch giảm 10%, trong khi kháng &lt;color=Ice&gt;Glacio RES&lt;/color&gt; và &lt;color=Thunder&gt;Electro RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Wind&gt;Aero&lt;/color&gt; và &lt;color=Light&gt;Spectro&lt;/color&gt; của kẻ địch giảm 10%, trong khi kháng &lt;color=Ice&gt;Glacio&lt;/color&gt; và &lt;color=Thunder&gt;Electro&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -15451,7 +15451,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; và &lt;color=Light&gt;Spectro RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và &lt;color=Dark&gt;Havoc RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; và &lt;color=Light&gt;Spectro&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; và &lt;color=Dark&gt;Havoc&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; và &lt;color=Light&gt;Spectro RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Wind&gt;Aero RES&lt;/color&gt; và &lt;color=Thunder&gt;Electro RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; và &lt;color=Light&gt;Spectro&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Wind&gt;Aero&lt;/color&gt; và &lt;color=Thunder&gt;Electro&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Kẻ địch bị giảm &lt;color=Fire&gt;Fusion RES&lt;/color&gt; và &lt;color=Light&gt;Spectro RES&lt;/color&gt; 10%, đồng thời tăng &lt;color=Wind&gt;Aero RES&lt;/color&gt; và &lt;color=Dark&gt;Havoc RES&lt;/color&gt; 10%.</t>
+          <t>Kẻ địch bị giảm &lt;color=Fire&gt;Kháng Fusion&lt;/color&gt; và &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; 10%, đồng thời tăng &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; và &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; 10%.</t>
         </is>
       </c>
     </row>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Resonators nhận 20% Tăng Sát Thương Resonance Skill. Mục tiêu trúng Resonance Skill sẽ chịu thêm &lt;color=Wind&gt;Aero DMG&lt;/color&gt; mỗi giây trong 18 giây.</t>
+          <t>Resonator nhận 20% Tăng Sát Thương Resonance Skill. Mục tiêu trúng Resonance Skill sẽ chịu thêm &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; mỗi giây trong 18 giây.</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Resonators nhận 30% Tăng Sát Thương Thuộc Tính.</t>
+          <t>Resonator nhận 30% Tăng Sát Thương Thuộc Tính.</t>
         </is>
       </c>
     </row>
@@ -15841,7 +15841,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Kích hoạt 1 Resonance Beacon</t>
+          <t>Kích hoạt 1 Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Chế độ Hợp tác</t>
+          <t>Chế độ Đồng Đội</t>
         </is>
       </c>
     </row>
@@ -16622,8 +16622,8 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Khi trang bị Công cụ này, bạn có thể nhảy từ độ cao nhất định để bay lượn và tăng tốc bằng cách tiêu hao một loại STA đặc biệt.
-Bạn cũng có thể bay khi đứng trên mặt đất. Khi ở trên mặt đất, hãy nhảy lên không trung để bắt đầu bay. Cooldown chiêu sẽ được áp dụng.</t>
+          <t>Khi trang bị Tiện Ích này, bạn có thể nhảy từ độ cao nhất định để bay lượn và tăng tốc bằng cách tiêu hao một loại STA đặc biệt.
+Bạn cũng có thể bay khi đứng trên mặt đất. Khi ở trên mặt đất, hãy nhảy lên không trung để bắt đầu bay. Thời gian hồi chiêu sẽ được áp dụng.</t>
         </is>
       </c>
     </row>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Khi gây sát thương, Crit. DMG của Resonator tăng 8% trong 10 giây, có thể chồng chất lên đến 3 lần. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Khi gây DMG, Crit. DMG của Resonator tăng 8% trong 10 giây, có thể chồng chất lên đến 3 lần. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Khi Tác Động Cuồng Nộ đạt tối đa, Havoc DMG tăng 40%.</t>
+          <t>Khi Tác Động Cuồng Nộ đạt tối đa, Sát Thương Havoc tăng 40%.</t>
         </is>
       </c>
     </row>
@@ -16818,7 +16818,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Khi gây sát thương, Tấn Công của Resonator tăng 6% trong 10 giây, có thể chồng chất lên đến 3 lần. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Khi gây DMG, ATK của Resonator tăng 6% trong 10 giây, có thể chồng chất lên đến 3 lần. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Gây sát thương làm tăng Energy Regen thêm 10% trong 10 giây, có thể chồng chất lên đến 3 lần. Hiệu ứng kích hoạt mỗi giây một lần.</t>
+          <t>Gây sát thương làm tăng Hồi Năng Lượng thêm 10% trong 10 giây, có thể chồng chất lên đến 3 lần. Hiệu ứng kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Khi Resonance Quá Tải đạt tối đa, Fusion DMG tăng thêm 40%.</t>
+          <t>Khi Cộng Hưởng Quá Tải đạt tối đa, Sát Thương Fusion tăng thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Gây Sát Thương sẽ tăng Tấn Công thêm 6% trong 10 giây, tối đa 3 lần tích lũy. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>Gây Sát Thương sẽ tăng ATK thêm 6% trong 10 giây, tối đa 3 lần tích lũy. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Khi Wind Surge đạt tối đa stack, Aero DMG tăng 40%.</t>
+          <t>Khi Wind Surge đạt tối đa stack, Sát Thương Aero tăng 40%.</t>
         </is>
       </c>
     </row>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Gây Sát Thương sẽ tăng Tấn Công của Resonator thêm 6% trong 10 giây, tối đa 3 lần tích lũy. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>Gây Sát Thương sẽ tăng ATK của Resonator thêm 6% trong 10 giây, tối đa 3 lần tích lũy. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -17273,7 +17273,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Khi Might Lửa Sao đạt tối đa, Fusion DMG tăng 40%.</t>
+          <t>Khi Might Lửa Sao đạt tối đa, Sát Thương Fusion tăng 40%.</t>
         </is>
       </c>
     </row>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Tiêu diệt kẻ địch sẽ tăng Tấn Công cho Resonators trong đội thêm 6% trong 10 giây, có thể chồng chất tối đa 3 lần.</t>
+          <t>Tiêu diệt kẻ địch sẽ tăng ATK cho các Resonator trong đội thêm 6% trong 10 giây, có thể chồng chất tối đa 3 lần.</t>
         </is>
       </c>
     </row>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Khi Overlapping Force đạt tối đa, Resonators trong đội nhận thêm 40% Spectro DMG Bonus.</t>
+          <t>Khi Lực Chồng Chất đạt tối đa, các Resonator trong đội nhận thêm 40% Tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Tiêu diệt kẻ địch sẽ tăng Tấn Công cho Resonators trong đội thêm 6% trong 10 giây, có thể chồng chất tối đa 3 lần.</t>
+          <t>Tiêu diệt kẻ địch sẽ tăng ATK cho các Resonator trong đội thêm 6% trong 10 giây, có thể chồng chất tối đa 3 lần.</t>
         </is>
       </c>
     </row>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Khi Overlapping Force đạt tối đa, Resonators trong đội nhận thêm 40% Fusion DMG Bonus.</t>
+          <t>Khi Lực Chồng Chất đạt tối đa, các Resonator trong đội nhận thêm 40% Tăng Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Tiêu diệt kẻ địch sẽ tăng Tấn Công cho Resonators trong đội thêm 6% trong 10 giây, có thể chồng chất tối đa 3 lần.</t>
+          <t>Tiêu diệt kẻ địch sẽ tăng ATK cho các Resonator trong đội thêm 6% trong 10 giây, có thể chồng chất tối đa 3 lần.</t>
         </is>
       </c>
     </row>
@@ -17663,7 +17663,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Khi Overlapping Force đạt tối đa, Resonators trong đội nhận thêm 40% Fusion DMG Bonus.</t>
+          <t>Khi Lực Chồng Chất đạt tối đa, các Resonator trong đội nhận thêm 40% Tăng Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Tiêu diệt kẻ địch sẽ tăng Tấn Công cho Resonators trong đội thêm 6% trong 10 giây, có thể chồng chất tối đa 3 lần.</t>
+          <t>Tiêu diệt kẻ địch sẽ tăng ATK cho các Resonator trong đội thêm 6% trong 10 giây, có thể chồng chất tối đa 3 lần.</t>
         </is>
       </c>
     </row>
@@ -17793,7 +17793,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Khi Overlapping Force đạt tối đa, Resonators trong đội nhận thêm 40% Aero DMG Bonus.</t>
+          <t>Khi Lực Chồng Chất đạt tối đa, các Resonator trong đội nhận thêm 40% Tăng Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -17858,7 +17858,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Tiêu diệt kẻ địch sẽ tăng Tấn Công cho Resonators trong đội thêm 6% trong 10 giây, có thể chồng chất tối đa 3 lần.</t>
+          <t>Tiêu diệt kẻ địch sẽ tăng ATK cho các Resonator trong đội thêm 6% trong 10 giây, có thể chồng chất tối đa 3 lần.</t>
         </is>
       </c>
     </row>
@@ -17923,7 +17923,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Khi Overlapping Force đạt tối đa, Resonators trong đội nhận thêm 40% Glacio DMG Bonus.</t>
+          <t>Khi Lực Chồng Chất đạt tối đa, các Resonator trong đội nhận thêm 40% Tăng Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -18207,7 +18207,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Thu thập Vật phẩm Phục hồi để hồi sinh Voidbane Eldertree</t>
+          <t>Thu thập Thuốc Phục Hồi để hồi sinh Cây Già Voidbane</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Khôi phục Cây Cổ Thụ Hóa Kỵ tại Sealed Fissure</t>
+          <t>Khôi phục Cây Cổ Thụ Hóa Kỵ tại Khe Nứt Bị Phong Ấn</t>
         </is>
       </c>
     </row>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Khuếch Đại DMG Kỹ Năng Echo</t>
+          <t>Khuếch Đại Sát Thương Kỹ Năng Âm Hưởng</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Thiếu buff Vũ khí</t>
+          <t>Chưa kích hoạt hiệu ứng vũ khí</t>
         </is>
       </c>
     </row>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Thiếu buff Vật phẩm</t>
+          <t>Thiếu hiệu ứng vật phẩm</t>
         </is>
       </c>
     </row>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Ở Lahai-Roi, Zip Zap có thể cảm nhận bất kỳ nhà thám hiểm Spacetrek nào gần đó bị bất động và phóng một &lt;color=Thunder&gt;Electric Shock&lt;/color&gt; để khôi phục trạng thái hoạt động bình thường cho họ. Ngoài ra, Zip Zap còn có thể phát hiện các đường dây điện bị hỏng trong phạm vi xung quanh và phóng một &lt;color=Thunder&gt;Electric Shock&lt;/color&gt; để tái kích hoạt đường dây.</t>
+          <t>Ở Lahai-Roi, Zip Zap có thể cảm nhận bất kỳ nhà thám hiểm Spacetrek nào gần đó bị bất động và phóng một &lt;color=Thunder&gt;Điện Giật&lt;/color&gt; để khôi phục trạng thái hoạt động bình thường cho họ. Ngoài ra, Zip Zap còn có thể phát hiện các đường dây điện bị hỏng trong phạm vi xung quanh và phóng một &lt;color=Thunder&gt;Điện Giật&lt;/color&gt; để tái kích hoạt đường dây.</t>
         </is>
       </c>
     </row>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Nhận toàn bộ hiệu ứng tăng sát thương từ Tăng Cường Phá Vỡ Giai Tune</t>
+          <t>Nhận toàn bộ hiệu ứng tăng DMG từ Tăng Cường Phá Vỡ Giai Điệu</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn chọn buff</t>
+          <t>Đã đạt giới hạn chọn Buff</t>
         </is>
       </c>
     </row>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Buff đã được chọn</t>
+          <t>Hiệu ứng đã được chọn</t>
         </is>
       </c>
     </row>
@@ -19446,7 +19446,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Khi Ember đạt tối đa, bước vào trạng thái Burning Waves, kẻ địch trúng đòn sẽ chịu thêm 60% Total Sát Thương trong 5 giây. Trạng thái này kéo dài 30 giây.</t>
+          <t>Khi Ember đạt tối đa, bước vào trạng thái Burning Waves, kẻ địch trúng đòn sẽ chịu thêm 60% Tổng Sát Thương trong 5 giây. Trạng thái này kéo dài 30 giây.</t>
         </is>
       </c>
     </row>
@@ -19513,9 +19513,9 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Gây sát thương hoặc tiêu diệt kẻ địch sẽ hồi phục Ember. 
+          <t>Gây DMG hoặc tiêu diệt kẻ địch sẽ hồi phục Ember. 
 Trạng thái Sóng Cháy kích hoạt khi Ember đầy, kéo dài trong 30 giây. Trong trạng thái này, mỗi đòn tấn công trúng kẻ địch sẽ khiến chúng chịu thêm 60% Sát Thương tổng trong 5 giây. 
-Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; rồi thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
+Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Sát Thương Phá Nhịp&lt;/color&gt; rồi thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19585,7 +19585,7 @@
       <c r="M292" t="inlineStr">
         <is>
           <t>Kẻ địch chịu thêm 30% tổng Sát Thương.
-Gây sát thương hoặc đánh bại kẻ địch sẽ hồi phục Ember.
+Gây DMG hoặc đánh bại kẻ địch sẽ hồi phục Ember.
 Trạng thái Burning Waves kích hoạt khi Ember đầy, kéo dài 30 giây. Trong trạng thái này, các đòn tấn công trúng kẻ địch sẽ khiến chúng chịu thêm 60% tổng Sát Thương trong 5 giây.
 Tất cả Mảnh có thể sử dụng không giới hạn khi ở trong Infinite Torrents.
 Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; và thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Thiết bị ghi tần số tiêu chuẩn dành cho tất cả thành viên Spacetrek Collective, chứa băng Rabelle để ghi lại liên tục các chỉ số sinh tồn của người đeo và dữ liệu môi trường xung quanh. Vỏ thiết bị được làm từ vật liệu có nguồn gốc từ Exostrider, giúp chống chịu một phần trước Void Storm.</t>
+          <t>Thiết bị ghi tần số tiêu chuẩn dành cho tất cả thành viên Spacetrek Collective, chứa băng Rabelle để ghi lại liên tục các chỉ số sinh tồn của người đeo và dữ liệu môi trường xung quanh. Vỏ thiết bị được làm từ vật liệu có nguồn gốc từ Exostrider, giúp chống chịu một phần trước Bão Hư Không.</t>
         </is>
       </c>
     </row>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Thiết bị ghi tần số tiêu chuẩn dành cho tất cả thành viên Spacetrek Collective, chứa băng Rabelle để ghi lại liên tục các chỉ số sinh tồn của người đeo và dữ liệu môi trường xung quanh. Vỏ thiết bị được làm từ vật liệu có nguồn gốc từ Exostrider, giúp chống chịu một phần trước Void Storm.</t>
+          <t>Thiết bị ghi tần số tiêu chuẩn dành cho tất cả thành viên Spacetrek Collective, chứa băng Rabelle để ghi lại liên tục các chỉ số sinh tồn của người đeo và dữ liệu môi trường xung quanh. Vỏ thiết bị được làm từ vật liệu có nguồn gốc từ Exostrider, giúp chống chịu một phần trước Bão Hư Không.</t>
         </is>
       </c>
     </row>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Hiện tại, việc sao chép tần số không chỉ là một kho lưu trữ thực tiễn mà còn là một nghi thức ghi chép, một hy vọng được giữ gìn. Ở Lahai-Roi, người ta gọi những ai biến mất trong Void Storm là "những kẻ lạc lối", và hy vọng một ngày họ sẽ trở về.</t>
+          <t>Hiện tại, việc sao chép tần số không chỉ là một kho lưu trữ thực tiễn mà còn là một nghi thức ghi chép, một hy vọng được giữ gìn. Ở Lahai-Roi, người ta gọi những ai biến mất trong Bão Hư Không là "những kẻ lạc lối", và hy vọng một ngày họ sẽ trở về.</t>
         </is>
       </c>
     </row>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Điểm mục tiêu không đủ</t>
+          <t>Điểm mục tiêu không đủ.</t>
         </is>
       </c>
     </row>
@@ -19978,7 +19978,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Hiyuki</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Hiyuki</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Fully activate Hiyuki's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Hiyuki ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Denia</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Denia</t>
         </is>
       </c>
     </row>
@@ -20173,7 +20173,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Fully activate Denia's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Denia ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -20373,9 +20373,9 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>&lt;color=Fire&gt;Fusion DMG&lt;/color&gt; gây ra bởi Resonators được tăng cường.
-&lt;color=Dark&gt;Havoc DMG&lt;/color&gt; mà kẻ địch phải chịu giảm đi.
-Một khu vực nguy hiểm sinh ra từ Waveworn Phenomenon. Đặc điểm nổi bật nhất là sợi dây Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Echo khổng lồ.
+          <t>&lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; gây ra bởi Resonator được tăng cường.
+&lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; mà kẻ địch phải chịu giảm đi.
+Một khu vực nguy hiểm sinh ra từ Waveworn Phenomenon. Đặc điểm nổi bật nhất là sợi dây Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn rất giàu tài nguyên quý giá.</t>
         </is>
       </c>
@@ -20444,9 +20444,9 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=Wind&gt;Aero DMG&lt;/color&gt; của Resonator được tăng cường
-Sát thương &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; nhận vào từ kẻ địch bị giảm
-Một vùng nguy hiểm sinh ra từ Hiện Tượng Bị Sóng Ăn Mòn. Đặc điểm nổi bật nhất là sợi Resonance Cord trắng ở trung tâm, nơi có một Echo khổng lồ. 
+          <t>DMG &lt;color=Wind&gt;Aero&lt;/color&gt; của Resonator được tăng cường
+DMG &lt;color=Thunder&gt;Electro&lt;/color&gt; nhận vào từ kẻ địch bị giảm
+Một vùng nguy hiểm sinh ra từ Hiện Tượng Bị Sóng Ăn Mòn. Đặc điểm nổi bật nhất là sợi Dây Cộng Hưởng trắng ở trung tâm, nơi có một Tổ Tacet khổng lồ. 
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn chứa đựng vô số tài nguyên quý giá.</t>
         </is>
       </c>
@@ -20515,9 +20515,9 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>&lt;color=Fire&gt;Fusion DMG&lt;/color&gt; gây ra bởi Resonators được tăng cường.
-&lt;color=Light&gt;Spectro DMG&lt;/color&gt; mà kẻ địch phải chịu giảm đi.
-Một khu vực nguy hiểm sinh ra từ Waveworn Phenomenon. Đặc điểm nổi bật nhất là sợi dây Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Echo khổng lồ.
+          <t>&lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; gây ra bởi Resonator được tăng cường.
+&lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; mà kẻ địch phải chịu giảm đi.
+Một khu vực nguy hiểm sinh ra từ Waveworn Phenomenon. Đặc điểm nổi bật nhất là sợi dây Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn rất giàu tài nguyên quý giá.</t>
         </is>
       </c>
@@ -20586,9 +20586,9 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>&lt;color=Fire&gt;Fusion DMG&lt;/color&gt; gây ra bởi Resonators được tăng cường.
-&lt;color=Dark&gt;Havoc DMG&lt;/color&gt; mà kẻ địch phải chịu giảm đi.
-Một khu vực nguy hiểm sinh ra từ Waveworn Phenomenon. Đặc điểm nổi bật nhất là sợi dây Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Echo khổng lồ.
+          <t>&lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; gây ra bởi Resonator được tăng cường.
+&lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; mà kẻ địch phải chịu giảm đi.
+Một khu vực nguy hiểm sinh ra từ Waveworn Phenomenon. Đặc điểm nổi bật nhất là sợi dây Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn rất giàu tài nguyên quý giá.</t>
         </is>
       </c>
@@ -20657,8 +20657,8 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Tăng &lt;color=Light&gt;Spectro DMG&lt;/color&gt; gây ra bởi Resonators. Giảm &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; nhận từ kẻ địch.
-Một khu vực nguy hiểm sinh ra từ Hiện Tượng Waveworn. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Echo khổng lồ.
+          <t>Tăng &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; gây ra bởi Resonator. Giảm &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; nhận từ kẻ địch.
+Một khu vực nguy hiểm sinh ra từ Hiện Tượng Waveworn. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, được đánh dấu bởi một Tổ Tacet khổng lồ.
 Ngoài các Tacet Discord nguy hiểm, khu vực này còn rất giàu tài nguyên quý giá.</t>
         </is>
       </c>
@@ -20727,9 +20727,9 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>&lt;color=Fire&gt;Fusion DMG&lt;/color&gt; gây ra bởi Resonators được tăng cường.
-&lt;color=Ice&gt;Glacio DMG&lt;/color&gt; mà kẻ địch phải chịu được giảm bớt.
-Một khu vực nguy hiểm sinh ra từ Waveworn Phenomenon. Đặc điểm nổi bật nhất là sợi dây Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Echo khổng lồ.
+          <t>&lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; gây ra bởi Resonator được tăng cường.
+&lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; mà kẻ địch phải chịu được giảm bớt.
+Một khu vực nguy hiểm sinh ra từ Waveworn Phenomenon. Đặc điểm nổi bật nhất là sợi dây Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn rất giàu tài nguyên quý giá.</t>
         </is>
       </c>
@@ -20798,9 +20798,9 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=Wind&gt;Aero DMG&lt;/color&gt; gây ra bởi Resonators được tăng cường.
-Sát thương &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; mà kẻ địch phải chịu giảm đi.
-Một khu vực nguy hiểm sinh ra từ Hiện Tượng Waveworn. Đặc điểm nổi bật nhất là sợi Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Echo khổng lồ.
+          <t>DMG &lt;color=Wind&gt;Aero&lt;/color&gt; gây ra bởi Resonator được tăng cường.
+DMG &lt;color=Thunder&gt;Electro&lt;/color&gt; mà kẻ địch phải chịu giảm đi.
+Một khu vực nguy hiểm sinh ra từ Hiện Tượng Waveworn. Đặc điểm nổi bật nhất là sợi Dây Cộng Hưởng trắng ở trung tâm, được đánh dấu bởi một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn rất giàu tài nguyên quý giá.</t>
         </is>
       </c>
@@ -20868,8 +20868,8 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Tăng &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; gây ra bởi Resonators. Giảm &lt;color=Light&gt;Spectro DMG&lt;/color&gt; nhận từ kẻ địch.
-Một khu vực nguy hiểm sinh ra từ Hiện Tượng Waveworn. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, được đánh dấu bởi một Echo khổng lồ.
+          <t>Tăng &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; gây ra bởi Resonator. Giảm &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; nhận từ kẻ địch.
+Một khu vực nguy hiểm sinh ra từ Hiện Tượng Waveworn. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, được đánh dấu bởi một Tổ Tacet khổng lồ.
 Ngoài các Tacet Discord nguy hiểm, khu vực này còn rất giàu tài nguyên quý giá.</t>
         </is>
       </c>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Là một phần của mạng lưới thông tin sinh thái Resonance, Đèn Hiệu Resonance thu thập dữ liệu thực địa trong phạm vi nhỏ và truyền về Trung Tâm Resonance.</t>
+          <t>Là một phần của mạng lưới thông tin sinh thái Cộng Hưởng, Đèn Hiệu Cộng Hưởng thu thập dữ liệu thực địa trong phạm vi nhỏ và truyền về Trung Tâm Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -21065,7 +21065,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -21262,7 +21262,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -21327,7 +21327,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -21392,7 +21392,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -21587,7 +21587,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -21652,7 +21652,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Một Terminal đặc biệt do Fisalias và Hội phát triển, có khả năng mô phỏng những kẻ địch mạnh mẽ. Đồng Xu Trial thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Trial.</t>
+          <t>Một Thiết bị đầu cuối đặc biệt do Fisalias và Hội phát triển, có khả năng mô phỏng những kẻ địch mạnh mẽ. Đồng Xu Thử Thách thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -21785,9 +21785,9 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=HighlightB&gt;Intro Skill DMG&lt;/color&gt; của Resonator tăng
-Sát thương &lt;color=Light&gt;Spectro DMG&lt;/color&gt; nhận vào từ kẻ địch giảm
-Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, nơi có một Echo khổng lồ.
+          <t>DMG &lt;color=HighlightB&gt;Kỹ Năng Khởi Động&lt;/color&gt; của Resonator tăng
+DMG &lt;color=Light&gt;Spectro&lt;/color&gt; nhận vào từ kẻ địch giảm
+Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, nơi có một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn chứa nhiều tài nguyên quý giá.</t>
         </is>
       </c>
@@ -21856,9 +21856,9 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=Wind&gt;Aero DMG&lt;/color&gt; của Resonator tăng
-Sát thương &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; nhận vào từ kẻ địch giảm
-Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, nơi có một Echo khổng lồ.
+          <t>DMG &lt;color=Wind&gt;Aero&lt;/color&gt; của Resonator tăng
+DMG &lt;color=Thunder&gt;Electro&lt;/color&gt; nhận vào từ kẻ địch giảm
+Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, nơi có một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn chứa nhiều tài nguyên quý giá.</t>
         </is>
       </c>
@@ -21927,9 +21927,9 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; của Resonator tăng
-Sát thương &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; nhận vào từ kẻ địch giảm
-Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, nơi có một Echo khổng lồ.
+          <t>DMG &lt;color=Ice&gt;Glacio&lt;/color&gt; của Resonator tăng
+DMG &lt;color=Fire&gt;Fusion&lt;/color&gt; nhận vào từ kẻ địch giảm
+Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, nơi có một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn chứa nhiều tài nguyên quý giá.</t>
         </is>
       </c>
@@ -21998,9 +21998,9 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; của Resonator tăng
-Sát thương &lt;color=Wind&gt;Aero DMG&lt;/color&gt; nhận vào từ kẻ địch giảm
-Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, nơi có một Echo khổng lồ.
+          <t>DMG &lt;color=Thunder&gt;Electro&lt;/color&gt; của Resonator tăng
+DMG &lt;color=Wind&gt;Aero&lt;/color&gt; nhận vào từ kẻ địch giảm
+Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, nơi có một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn chứa nhiều tài nguyên quý giá.</t>
         </is>
       </c>
@@ -22069,9 +22069,9 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; của Resonator tăng
-Sát thương &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; nhận vào từ kẻ địch giảm
-Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, nơi có một Echo khổng lồ.
+          <t>DMG &lt;color=Fire&gt;Fusion&lt;/color&gt; của Resonator tăng
+DMG &lt;color=Ice&gt;Glacio&lt;/color&gt; nhận vào từ kẻ địch giảm
+Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, nơi có một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn chứa nhiều tài nguyên quý giá.</t>
         </is>
       </c>
@@ -22140,9 +22140,9 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; của Resonator tăng
-Sát thương &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; nhận vào từ kẻ địch giảm
-Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, nơi có một Echo khổng lồ.
+          <t>DMG &lt;color=Thunder&gt;Electro&lt;/color&gt; của Resonator tăng
+DMG &lt;color=Dark&gt;Havoc&lt;/color&gt; nhận vào từ kẻ địch giảm
+Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, nơi có một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn chứa nhiều tài nguyên quý giá.</t>
         </is>
       </c>
@@ -22211,9 +22211,9 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=Wind&gt;Aero DMG&lt;/color&gt; của Resonator tăng
-Sát thương &lt;color=Light&gt;Spectro DMG&lt;/color&gt; nhận vào từ kẻ địch giảm
-Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, nơi có một Echo khổng lồ.
+          <t>DMG &lt;color=Wind&gt;Aero&lt;/color&gt; của Resonator tăng
+DMG &lt;color=Light&gt;Spectro&lt;/color&gt; nhận vào từ kẻ địch giảm
+Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, nơi có một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn chứa nhiều tài nguyên quý giá.</t>
         </is>
       </c>
@@ -22282,9 +22282,9 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; của Resonator tăng
-Sát thương &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; nhận vào từ kẻ địch giảm.
-Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, nơi có một Echo khổng lồ.
+          <t>DMG &lt;color=Ice&gt;Glacio&lt;/color&gt; của Resonator tăng
+DMG &lt;color=Fire&gt;Fusion&lt;/color&gt; nhận vào từ kẻ địch giảm.
+Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, nơi có một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn chứa nhiều tài nguyên quý giá.</t>
         </is>
       </c>
@@ -22353,9 +22353,9 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Sát thương &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; của Resonator tăng
-Sát thương &lt;color=Wind&gt;Aero DMG&lt;/color&gt; nhận vào từ kẻ địch giảm
-Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Resonance Cord trắng ở trung tâm, nơi có một Echo khổng lồ.
+          <t>DMG &lt;color=Dark&gt;Havoc&lt;/color&gt; của Resonator tăng
+DMG &lt;color=Wind&gt;Aero&lt;/color&gt; nhận vào từ kẻ địch giảm
+Một vùng nguy hiểm sinh ra từ Hiện Tượng Bào Mòn Sóng. Đặc điểm nổi bật nhất là Dây Cộng Hưởng trắng ở trung tâm, nơi có một Tổ Tacet khổng lồ.
 Ngoài những Tacet Discord nguy hiểm, khu vực này còn chứa nhiều tài nguyên quý giá.</t>
         </is>
       </c>
@@ -22424,8 +22424,8 @@
       <c r="M334" t="inlineStr">
         <is>
           <t>&lt;color=Dark&gt;[Havoc]&lt;/color&gt;
-Có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; đối với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;
-Một Discord thì thầm, sinh ra ngoài Gorges of Spirits. Nó hiện thân cho một chiến binh u ám, báo trước xung đột và đau khổ vĩnh cửu trong sự hiện diện đen tối của mình.</t>
+Có &lt;color=HighlightB&gt;Kháng Tăng&lt;/color&gt; đối với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;
+Một Tacet Discord thì thầm, sinh ra ngoài Gorges of Spirits. Nó hiện thân cho một chiến binh u ám, báo trước xung đột và đau khổ vĩnh cửu trong sự hiện diện đen tối của mình.</t>
         </is>
       </c>
     </row>
@@ -22493,7 +22493,7 @@
       <c r="M335" t="inlineStr">
         <is>
           <t>&lt;color=Ice&gt;[Glacio]&lt;/color&gt;
-Có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; cao hơn đối với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;
+Có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;
 Sinh vật đột biến cổ đại sống sâu trong Gorge of Spirits, chiếc chuông cổ trên lưng chúng có thể phát ra sóng âm cực kỳ chết người khi rung lên.</t>
         </is>
       </c>
@@ -22562,8 +22562,8 @@
       <c r="M336" t="inlineStr">
         <is>
           <t>&lt;color=Thunder&gt;[Electro]&lt;/color&gt;
-Có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; đối với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;
-Một Discord mạnh mẽ xuất hiện tại Tacet Field của Desorock Highland, có khả năng sử dụng sức mạnh của Electro.</t>
+Có &lt;color=HighlightB&gt;kháng tăng&lt;/color&gt; đối với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;
+Một Tacet Discord mạnh mẽ xuất hiện tại Tổ Tacet của Desorock Highlands, có khả năng sử dụng sức mạnh của Electro.</t>
         </is>
       </c>
     </row>
@@ -22631,8 +22631,8 @@
       <c r="M337" t="inlineStr">
         <is>
           <t>&lt;color=Fire&gt;[Fusion]&lt;/color&gt;
-Đã &lt;color=HighlightB&gt;increased RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;
-Một Discord mạnh mẽ nằm tại Thành phố Cảng Guixu. Theo lời nhân chứng, chuyển động của nó khác biệt so với các TD khác, cần nghiên cứu thêm để có thông tin chi tiết hơn.</t>
+Đã &lt;color=HighlightB&gt;tăng Kháng&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;
+Một Tacet Discord mạnh mẽ nằm tại Thành phố Cảng Guixu. Theo lời nhân chứng, chuyển động của nó khác biệt so với các TD khác, cần nghiên cứu thêm để có thông tin chi tiết hơn.</t>
         </is>
       </c>
     </row>
@@ -22700,8 +22700,8 @@
       <c r="M338" t="inlineStr">
         <is>
           <t>&lt;color=Wind&gt;[Aero]&lt;/color&gt;
-Có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; tăng cường.
-Một Sinh Vật Đột Biến đáng gờm trong lòng Giant Banyan. Thủ lĩnh của tộc Hoochief.</t>
+Có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; tăng cường.
+Một Sinh Vật Đột Biến đáng gờm trong lòng Cây Đa Khổng Lồ. Thủ lĩnh của tộc Hoochief.</t>
         </is>
       </c>
     </row>
@@ -22769,8 +22769,8 @@
       <c r="M339" t="inlineStr">
         <is>
           <t>&lt;color=Light&gt;[Spectro]&lt;/color&gt;
-Có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; cao hơn đối với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;
-Một Discord đáng gờm làm tổ tại Whining Aix's Mire, tiếng gào thét của nó được người dân Huanglong gọi là "Khúc bi ca bất tận".</t>
+Có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;
+Một Tacet Discord đáng gờm làm tổ tại Whining Aix's Mire, tiếng gào thét của nó được người dân Huanglong gọi là "Khúc bi ca bất tận".</t>
         </is>
       </c>
     </row>
@@ -22838,7 +22838,7 @@
       <c r="M340" t="inlineStr">
         <is>
           <t>&lt;color=Dark&gt;[Havoc]&lt;/color&gt;
-Có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; đối với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+Có &lt;color=HighlightB&gt;Kháng Tăng&lt;/color&gt; đối với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Quái chim khổng lồ giả dạng cư ngụ tại Desorock Highland, với ba đầu, mỗi đầu đảm nhiệm việc ăn, tấn công và bảo vệ.</t>
         </is>
       </c>
@@ -22907,8 +22907,8 @@
       <c r="M341" t="inlineStr">
         <is>
           <t>&lt;color=Thunder&gt;[Electro]&lt;/color&gt;
-Có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; đối với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Sinh ra từ phòng thí nghiệm Discord của Court of Savantae, nó không ngừng tiến hóa trong quá trình nuốt chửng Echo, trở nên ngày càng đồ sộ.</t>
+Có &lt;color=HighlightB&gt;kháng tăng&lt;/color&gt; đối với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Sinh ra từ phòng thí nghiệm Tacet Discord của Court of Savantae, nó không ngừng tiến hóa trong quá trình nuốt chửng Echo, trở nên ngày càng đồ sộ.</t>
         </is>
       </c>
     </row>
@@ -22976,8 +22976,8 @@
       <c r="M342" t="inlineStr">
         <is>
           <t>&lt;color=Thunder&gt;[Electro]&lt;/color&gt;
-Có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; đối với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Discord hùng mạnh lang thang trên Central Plains, điều khiển sức mạnh bão tố để liên tục nuốt chửng âm thanh bảo vệ con người, được coi là một trong những tiên phong của Crownless.</t>
+Có &lt;color=HighlightB&gt;kháng tăng&lt;/color&gt; đối với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Tacet Discord hùng mạnh lang thang trên Central Plains, điều khiển sức mạnh bão tố để liên tục nuốt chửng âm thanh bảo vệ con người, được coi là một trong những tiên phong của Crownless.</t>
         </is>
       </c>
     </row>
@@ -23045,8 +23045,8 @@
       <c r="M343" t="inlineStr">
         <is>
           <t>&lt;color=Ice&gt;[Glacio]&lt;/color&gt;
-Có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; cao hơn đối với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Một Discord mạnh mẽ trú ngụ trong các hầm sâu của Tiger's Maw. Rất ít báo cáo về việc nhìn thấy chúng, tất cả đều cho rằng chúng giống côn trùng.</t>
+Có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Một Tacet Discord mạnh mẽ trú ngụ trong các hầm sâu của Tiger's Maw. Rất ít báo cáo về việc nhìn thấy chúng, tất cả đều cho rằng chúng giống côn trùng.</t>
         </is>
       </c>
     </row>
@@ -23114,8 +23114,8 @@
       <c r="M344" t="inlineStr">
         <is>
           <t>&lt;color=Light&gt;[Spectro]&lt;/color&gt;
-Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; cao hơn đối với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Hàng phòng thủ cuối cùng do Tethys Hệ thống xây dựng, tuần tra biên giới giữa thế giới thực và thế giới số.</t>
+Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+Hàng phòng thủ cuối cùng do Hệ Thống Tethys xây dựng, tuần tra biên giới giữa thế giới thực và thế giới số.</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Tacet Field cấp độ đe dọa trung bình. Defeat the Tacet Discords ẩn nấp bên trong để nhận Thuốc Resonance và vật liệu nâng cấp Resonator.</t>
+          <t>Tổ Tacet cấp độ đe dọa trung bình. Hạ gục các Tacet Discord ẩn nấp bên trong để nhận Thuốc Cộng Hưởng và vật liệu nâng cấp Resonator.</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23375,7 +23375,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23440,7 +23440,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23505,7 +23505,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23895,7 +23895,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23960,7 +23960,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24025,7 +24025,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24090,7 +24090,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24285,7 +24285,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24350,7 +24350,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24415,7 +24415,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24545,7 +24545,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24610,7 +24610,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24740,7 +24740,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24805,7 +24805,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24870,7 +24870,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24935,7 +24935,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25000,7 +25000,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25260,7 +25260,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25325,7 +25325,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25390,7 +25390,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25455,7 +25455,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25520,7 +25520,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25650,7 +25650,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25715,7 +25715,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25780,7 +25780,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25845,7 +25845,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25975,7 +25975,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Nhờ dữ liệu vị trí của trạm cơ sở Đèn Tín Hiệu Resonance, Waypoint sẽ tự hiệu chỉnh để giúp người dùng đến được vị trí đã đánh dấu.</t>
+          <t>Nhờ dữ liệu vị trí của trạm cơ sở Đèn Tín Hiệu Cộng Hưởng, Điểm Dẫn Đường sẽ tự hiệu chỉnh để giúp người dùng đến được vị trí đã đánh dấu.</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Resonators thuộc hệ &lt;color=Wind&gt;Aero&lt;/color&gt; và &lt;color=Light&gt;Spectro&lt;/color&gt; gây thêm sát thương khi sử dụng &lt;color=highlight&gt;Intro Skills&lt;/color&gt;.</t>
+          <t>Resonator thuộc hệ &lt;color=Wind&gt;Aero&lt;/color&gt; và &lt;color=Light&gt;Spectro&lt;/color&gt; gây thêm sát thương khi sử dụng &lt;color=highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26105,7 +26105,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Resonators thuộc hệ &lt;color=Ice&gt;Glacio&lt;/color&gt; và &lt;color=Dark&gt;Havoc&lt;/color&gt; gây thêm sát thương khi sử dụng &lt;color=highlight&gt;Intro Skills&lt;/color&gt;.</t>
+          <t>Resonator thuộc hệ &lt;color=Ice&gt;Glacio&lt;/color&gt; và &lt;color=Dark&gt;Havoc&lt;/color&gt; gây thêm sát thương khi sử dụng &lt;color=highlight&gt;Kỹ Năng Intro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26170,7 +26170,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Resonators &lt;color=Fire&gt;Fusion&lt;/color&gt; và &lt;color=Thunder&gt;Electro&lt;/color&gt; gây thêm sát thương khi sử dụng &lt;color=highlight&gt;Intro Skills&lt;/color&gt;.</t>
+          <t>Resonator &lt;color=Fire&gt;Fusion&lt;/color&gt; và &lt;color=Thunder&gt;Electro&lt;/color&gt; gây thêm sát thương khi sử dụng &lt;color=highlight&gt;Kỹ Năng Intro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26235,7 +26235,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Resonators phục hồi toàn bộ &lt;color=highlight&gt;Resonance Energy&lt;/color&gt; sau khi sử dụng &lt;color=highlight&gt;Intro Skills&lt;/color&gt;.</t>
+          <t>Resonator phục hồi toàn bộ &lt;color=highlight&gt;Resonance Energy&lt;/color&gt; sau khi sử dụng &lt;color=highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26300,7 +26300,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Crit. DMG của Resonators tăng sau khi sử dụng &lt;color=highlight&gt;Intro Skills&lt;/color&gt;.</t>
+          <t>Crit. DMG của Resonator tăng sau khi sử dụng &lt;color=highlight&gt;Kỹ Năng Intro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26365,7 +26365,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt; sẽ đặt lại Cooldown chiêu của &lt;color=highlight&gt;Echo Skills&lt;/color&gt; đang hoạt động.</t>
+          <t>Sử dụng &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt; sẽ đặt lại thời gian hồi chiêu của &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt; đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -26430,7 +26430,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=highlight&gt;Heavy Attack&lt;/color&gt; sẽ giảm Cooldown chiêu của &lt;color=highlight&gt;Echo Skills&lt;/color&gt; đang hoạt động.</t>
+          <t>Sử dụng &lt;color=highlight&gt;Heavy Attack&lt;/color&gt; sẽ giảm thời gian hồi chiêu của &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt; đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=highlight&gt;Echo Skills&lt;/color&gt;, tăng sát thương của Heavy Attack và Resonance Skill.</t>
+          <t>Khi sử dụng &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt;, tăng DMG của Đòn Heavy Attack và Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=highlight&gt;Echo Skills&lt;/color&gt;, &lt;color=highlight&gt;Intro Skills&lt;/color&gt; không cần Cooldown chiêu.</t>
+          <t>Sau khi sử dụng &lt;color=highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt;, &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt; không cần thời gian hồi chiêu.</t>
         </is>
       </c>
     </row>
@@ -26690,7 +26690,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Những Nightmares từ vực sâu giấc mơ trỗi dậy trong "Ký Ức Chiến Bại", gieo rắc sự tha hóa vào tâm trí kẻ mộng du. Kẻ địch sẽ cực kỳ nguy hiểm, và Resonator sẽ chịu sát thương mỗi giây.</t>
+          <t>Những Ác Mộng từ vực sâu giấc mơ trỗi dậy trong "Ký Ức Chiến Bại", gieo rắc sự tha hóa vào tâm trí kẻ mộng du. Kẻ địch sẽ cực kỳ nguy hiểm, và Resonator sẽ chịu sát thương mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Khi gây sát thương, tăng toàn bộ Sát Thương Thuộc Tính của nhân vật lên {0}% trong {1} giây, có thể chồng chất lên đến {2} lần. Hiệu ứng này chỉ có thể kích hoạt {4} lần mỗi {3} giây.</t>
+          <t>Khi gây DMG, tăng toàn bộ Sát Thương Thuộc Tính của nhân vật lên {0}% trong {1} giây, có thể chồng chất lên đến {2} lần. Hiệu ứng này chỉ có thể kích hoạt {4} lần mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -26885,7 +26885,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Khi Dodge, phục hồi {0} Concerto Energy và {1} Resonance Energy cho bản thân, đồng thời tăng Tấn Công của đội lên {2}% trong {3} giây, có thể tích lũy tối đa {4} lần.</t>
+          <t>Khi né tránh, phục hồi {0} Năng Lượng Concerto và {1} Resonance Energy cho bản thân, đồng thời tăng ATK của đội lên {2}% trong {3} giây, có thể tích lũy tối đa {4} lần.</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Khi sử dụng Intro Skill, phục hồi {0} Resonance Energy cho bản thân và tăng {1}% Tấn Công cho cả đội trong {2} giây, có thể tích lũy tối đa {3} lần.</t>
+          <t>Khi sử dụng Kỹ Năng Khởi Động, phục hồi {0} Resonance Energy cho bản thân và tăng {1}% ATK cho cả đội trong {2} giây, có thể tích lũy tối đa {3} lần.</t>
         </is>
       </c>
     </row>
@@ -27080,7 +27080,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Khi hồi phục đồng đội, tăng Tấn Công của đội lên {0}% trong {1} giây, chồng chất tối đa {2} lần. Hiệu ứng này có thể kích hoạt {3} lần mỗi giây.</t>
+          <t>Khi hồi phục đồng đội, tăng ATK của đội lên {0}% trong {1} giây, chồng chất tối đa {2} lần. Hiệu ứng này có thể kích hoạt {3} lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -27210,7 +27210,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Khi sử dụng Resonance Liberation, tăng {0}% Energy Regen và Tấn Công cho cả đội trong {1} giây, có thể tích lũy tối đa {2} lần.</t>
+          <t>Khi sử dụng Resonance Liberation, tăng {0}% Hồi Năng Lượng và ATK cho cả đội trong {1} giây, có thể tích lũy tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -27275,7 +27275,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Khi Dodge, tăng Tấn Công của toàn đội thêm {0}% trong {1} giây, tối đa {2} lần cộng dồn. Tất cả cộng dồn sẽ bị xóa khi nhân vật chịu sát thương.</t>
+          <t>Khi né tránh, tăng ATK của toàn đội thêm {0}% trong {1} giây, tối đa {2} lần cộng dồn. Tất cả cộng dồn sẽ bị xóa khi nhân vật chịu sát thương.</t>
         </is>
       </c>
     </row>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Kích hoạt Heavy Attack tăng Sát Thương cho Resonators trong đội lên {0}% trong {1} giây, tối đa {2} lần. Hiệu ứng này chỉ kích hoạt {4} lần mỗi {3} giây.</t>
+          <t>Kích hoạt Heavy Attack tăng Sát Thương cho các Resonator trong đội lên {0}% trong {1} giây, tối đa {2} lần. Hiệu ứng này chỉ kích hoạt {4} lần mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Increase Electro DMG thêm {0}%. Khi gây sát thương, đồng thời tăng Electro DMG thêm {1}% trong {2} giây. Hiệu ứng này có thể kích hoạt {3} lần mỗi giây và tối đa {4} lớp.</t>
+          <t>Tăng Sát Thương Electro thêm {0}%. Khi gây DMG, đồng thời tăng Sát Thương Electro thêm {1}% trong {2} giây. Hiệu ứng này có thể kích hoạt {3} lần mỗi giây và tối đa {4} lớp.</t>
         </is>
       </c>
     </row>
@@ -27470,7 +27470,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Increase Spectro DMG thêm {0}%. Bonus này giảm {2}% sau mỗi {1} giây cho đến khi còn {3}%. Khi sử dụng Resonance Liberation, tăng thêm Spectro DMG {4}%, tối đa {5}%.</t>
+          <t>Tăng Sát Thương Spectro thêm {0}%. Bonus này giảm {2}% sau mỗi {1} giây cho đến khi còn {3}%. Khi sử dụng Resonance Liberation, tăng thêm Sát Thương Spectro {4}%, tối đa {5}%.</t>
         </is>
       </c>
     </row>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Khi sử dụng Resonance Skill, Resonators trong đội nhận được Hưởng Ứng. Khi đạt {0} tầng Hưởng Ứng, xóa toàn bộ tầng và tăng Tấn Công của Resonators trong đội thêm {1}% trong {2} giây.</t>
+          <t>Khi sử dụng Resonance Skill, Resonator trong đội nhận được Hưởng Ứng. Khi đạt {0} tầng Hưởng Ứng, xóa toàn bộ tầng và tăng ATK của Resonator trong đội thêm {1}% trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -27600,7 +27600,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ hồi phục {0} Resonance Energy. Có thể kích hoạt {2} lần mỗi {1} giây.</t>
+          <t>Né thành công sẽ hồi phục {0} Resonance Energy. Có thể kích hoạt {2} lần mỗi {1} giây.</t>
         </is>
       </c>
     </row>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Khi một đòn Basic Attack gây sát thương, hiệu ứng tăng Sát Thương Resonance Skill của tất cả Resonators trong đội sẽ tăng thêm {0}% trong {1} giây, có thể chồng chất tối đa {2} lần.</t>
+          <t>Khi một đòn Basic Attack gây DMG, hiệu ứng tăng Sát Thương Resonance Skill của tất cả Resonator trong đội sẽ tăng thêm {0}% trong {1} giây, có thể chồng chất tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -27730,7 +27730,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Increase Sát Thương Hệ Fusion thêm {0}%. Khi Basic Attack gây sát thương, tăng thêm Sát Thương Hệ Fusion của bản thân {1}% trong {2} giây. Hiệu ứng này có thể chồng chất lên đến {3} lần.</t>
+          <t>Tăng Sát Thương Hệ Fusion thêm {0}%. Khi Đòn Cơ Bản gây DMG, tăng thêm Sát Thương Hệ Fusion của bản thân {1}% trong {2} giây. Hiệu ứng này có thể chồng chất lên đến {3} lần.</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Khi hồi phục một Resonators trong đội, tăng Tấn Công của Resonators trong đội lên {0}% trong {1} giây. Hiệu ứng này có thể kích hoạt {2} lần mỗi giây và tối đa {3} lớp.</t>
+          <t>Khi hồi phục một Resonator trong đội, tăng ATK của các Resonator trong đội lên {0}% trong {1} giây. Hiệu ứng này có thể kích hoạt {2} lần mỗi giây và tối đa {3} lớp.</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Khi phản công, tăng sát thương của Resonators trong đội lên {0}% trong {1} giây.</t>
+          <t>Khi phản công, tăng sát thương của các Resonator trong đội lên {0}% trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -27925,7 +27925,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Khi Dodge thành công, Tấn Công của bản thân tăng {0}% trong {1} giây, tối đa {2} lần cộng dồn. Tất cả cộng dồn sẽ bị xóa khi nhận sát thương.</t>
+          <t>Khi né tránh thành công, ATK của bản thân tăng {0}% trong {1} giây, tối đa {2} lần cộng dồn. Tất cả cộng dồn sẽ bị xóa khi nhận sát thương.</t>
         </is>
       </c>
     </row>
@@ -27990,7 +27990,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Khi sử dụng Resonance Skill, Tấn Công của Resonators trong đội tăng {0}% trong {1} giây, có thể tích lũy tối đa {2} lần.</t>
+          <t>Khi sử dụng Resonance Skill, ATK của Resonator trong đội tăng {0}% trong {1} giây, có thể tích lũy tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -28055,7 +28055,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Increase Aero DMG thêm {0}%. Hiệu ứng này giảm {2}% mỗi {1} giây cho đến khi còn {3}%. Khi kích hoạt Resonance Liberation, tăng thêm Aero DMG {4}%, tối đa {5}%.</t>
+          <t>Tăng Sát Thương Aero thêm {0}%. Hiệu ứng này giảm {2}% mỗi {1} giây cho đến khi còn {3}%. Khi kích hoạt Resonance Liberation, tăng thêm Sát Thương Aero {4}%, tối đa {5}%.</t>
         </is>
       </c>
     </row>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Khi sử dụng Resonance Liberation, tăng {0}% Tấn Công cho Resonators trong đội và phục hồi {1} Resonance Energy. Hiệu ứng này chỉ có thể kích hoạt {3} lần mỗi {2} giây. Có thể tích lũy tối đa {4} lần.</t>
+          <t>Khi sử dụng Resonance Liberation, tăng {0}% ATK cho các Resonator trong đội và phục hồi {1} Resonance Energy. Hiệu ứng này chỉ có thể kích hoạt {3} lần mỗi {2} giây. Có thể tích lũy tối đa {4} lần.</t>
         </is>
       </c>
     </row>
@@ -28185,7 +28185,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Buff Chiến Thuật Simulacra New Được Mở Khóa</t>
+          <t>Buff Chiến Thuật Simulacra Mới Được Mở Khóa</t>
         </is>
       </c>
     </row>
@@ -28250,7 +28250,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Giảm Cooldown Kéo</t>
+          <t>Giảm Thời gian hồi Móc</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Increase tốc độ di chuyển.</t>
+          <t>Tăng tốc độ di chuyển.</t>
         </is>
       </c>
     </row>
@@ -28380,7 +28380,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Increase Tấn Công cho tất cả thành viên trong đội thêm 600.</t>
+          <t>Tăng ATK cho tất cả thành viên trong đội thêm 600.</t>
         </is>
       </c>
     </row>
@@ -28445,7 +28445,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Increase Sát Thương cho tất cả thành viên trong đội thêm 45%.</t>
+          <t>Tăng Sát Thương cho tất cả thành viên trong đội thêm 45%.</t>
         </is>
       </c>
     </row>
@@ -28510,7 +28510,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate thêm 10% cho toàn đội.</t>
+          <t>Tăng Crit. Rate thêm 10% cho toàn đội.</t>
         </is>
       </c>
     </row>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Increase Crit. DMG thêm 20% cho toàn đội.</t>
+          <t>Tăng Crit. DMG thêm 20% cho toàn đội.</t>
         </is>
       </c>
     </row>
@@ -28705,7 +28705,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Summon thêm đạn khi Đòn Hạ Gục trúng mục tiêu.</t>
+          <t>Triệu hồi thêm đạn khi Đòn Hạ Gục trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Summon thêm đạn khi sử dụng Kỹ Năng Echo giữa không trung.</t>
+          <t>Triệu hồi thêm đạn khi sử dụng Kỹ Năng Echo giữa không trung.</t>
         </is>
       </c>
     </row>
@@ -28835,7 +28835,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Increase chỉ số mỗi giây khi ở trên không.</t>
+          <t>Tăng chỉ số mỗi giây khi ở trên không.</t>
         </is>
       </c>
     </row>
@@ -28900,7 +28900,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Trigger Dừng Thời Gian khi thi triển Kỹ Năng Echo trên mặt đất.</t>
+          <t>Kích hoạt Dừng Thời Gian khi thi triển Kỹ Năng Echo trên mặt đất.</t>
         </is>
       </c>
     </row>
@@ -28965,7 +28965,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Increase tốc độ di chuyển lên 50%. Lao nhanh sẽ đẩy lùi kẻ địch.</t>
+          <t>Tăng tốc độ di chuyển lên 50%. Lao nhanh sẽ đẩy lùi kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Increase tốc độ di chuyển.</t>
+          <t>Tăng tốc độ di chuyển.</t>
         </is>
       </c>
     </row>
@@ -29290,7 +29290,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Cooldown Móc giảm 50%.</t>
+          <t>Thời gian hồi Móc giảm 50%.</t>
         </is>
       </c>
     </row>
@@ -29556,7 +29556,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Sử dụng Intro Skill 1 lần</t>
+          <t>Mục tiêu 2: Sử dụng Kỹ Năng Khởi Động 1 lần</t>
         </is>
       </c>
     </row>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Gây sát thương bằng Resonance Liberation</t>
+          <t>Mục tiêu 3: Deal damage with Resonance Liberation</t>
         </is>
       </c>
     </row>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Tránh bị đóng băng bởi Glacio Chafe.</t>
+          <t>Mục tiêu 1: Avoid being frozen by Glacio Chafe</t>
         </is>
       </c>
     </row>
@@ -29751,7 +29751,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Dùng Sát Thương Intro Skill để hóa đá kẻ địch 1 lần</t>
+          <t>Mục tiêu 3: Dùng Sát Thương Kỹ Năng Khởi Động để hóa đá kẻ địch 1 lần</t>
         </is>
       </c>
     </row>
@@ -30076,7 +30076,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Sử dụng Intro Skill 4 lần</t>
+          <t>Mục tiêu 2: Sử dụng Kỹ Năng Khởi Động 4 lần</t>
         </is>
       </c>
     </row>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Dùng Sát Thương Intro Skill để hóa đá kẻ địch 1 lần</t>
+          <t>Mục tiêu 3: Dùng Sát Thương Kỹ Năng Khởi Động để hóa đá kẻ địch 1 lần</t>
         </is>
       </c>
     </row>
@@ -30531,7 +30531,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Sử dụng Intro Skill 4 lần</t>
+          <t>Mục tiêu 2: Sử dụng Kỹ Năng Khởi Động 4 lần</t>
         </is>
       </c>
     </row>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Successful Dodges&lt;/color&gt; gây Sát Thương Khu Vực và &lt;color=Highlight&gt;extend&lt;/color&gt; thời gian thử thách. Thực hiện &lt;color=Highlight&gt;Counterattacks&lt;/color&gt; sẽ &lt;color=Highlight&gt;greatly extends&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
+          <t>&lt;color=Highlight&gt;Né tránh thành công&lt;/color&gt; gây Sát Thương Khu Vực và &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách. Thực hiện &lt;color=Highlight&gt;Phản Đòn&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài đáng kể&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;bị tấn công&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
         </is>
       </c>
     </row>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Kẻ địch này rất mạnh. &lt;color=Highlight&gt;Successful Dodges&lt;/color&gt; sẽ gây Sát Thương diện rộng và &lt;color=Highlight&gt;extend&lt;/color&gt; thời gian thử thách. Thực hiện &lt;color=Highlight&gt;Counterattacks&lt;/color&gt; hoặc &lt;color=Highlight&gt;immobilizing the enemy&lt;/color&gt; sẽ &lt;color=Highlight&gt;greatly extends&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ rút ngắn thời gian.</t>
+          <t>Kẻ địch này rất mạnh. &lt;color=Highlight&gt;Né thành công&lt;/color&gt; sẽ gây Sát Thương diện rộng và &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách. Thực hiện &lt;color=Highlight&gt;Phản công&lt;/color&gt; hoặc &lt;color=Highlight&gt;Hóa Đá kẻ địch&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài đáng kể&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;bị tấn công&lt;/color&gt; sẽ rút ngắn thời gian.</t>
         </is>
       </c>
     </row>
@@ -31051,7 +31051,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Kẻ địch này cực kỳ mạnh. &lt;color=Highlight&gt;Successful Dodges&lt;/color&gt; sẽ gây sát thương diện rộng và &lt;color=Highlight&gt;extend&lt;/color&gt; thời gian thử thách. &lt;color=Highlight&gt;Counterattacks&lt;/color&gt; hoặc &lt;color=Highlight&gt;immobilizing enemies&lt;/color&gt; sẽ &lt;color=Highlight&gt;greatly extends&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
+          <t>Kẻ địch này cực kỳ mạnh. &lt;color=Highlight&gt;Né thành công&lt;/color&gt; sẽ gây DMG diện rộng và &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách. &lt;color=Highlight&gt;Phản công&lt;/color&gt; hoặc &lt;color=Highlight&gt;khống chế kẻ địch&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài đáng kể&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;bị tấn công&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
         </is>
       </c>
     </row>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Successful Dodges&lt;/color&gt; hoặc thực hiện &lt;color=Highlight&gt;Counterattacks&lt;/color&gt; sẽ &lt;color=Highlight&gt;extend&lt;/color&gt; thời gian thử thách. &lt;color=Highlight&gt;Defeating enemies&lt;/color&gt; sẽ phục hồi HP và &lt;color=Highlight&gt;greatly extends&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
+          <t>&lt;color=Highlight&gt;Né tránh thành công&lt;/color&gt; hoặc thực hiện &lt;color=Highlight&gt;Phản Đòn&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách. &lt;color=Highlight&gt;Đánh bại kẻ địch&lt;/color&gt; sẽ phục hồi HP và &lt;color=Highlight&gt;kéo dài đáng kể&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;bị tấn công&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
         </is>
       </c>
     </row>
@@ -31246,7 +31246,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Challenge I: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
+          <t>Thử Thách I: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
         </is>
       </c>
     </row>
@@ -31376,7 +31376,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Kẻ địch này rất mạnh. &lt;color=Highlight&gt;Successful Dodges&lt;/color&gt; hoặc &lt;color=Highlight&gt;Counterattacks&lt;/color&gt; sẽ &lt;color=Highlight&gt;extend&lt;/color&gt; thời gian thử thách. &lt;color=Highlight&gt;Defeating enemies&lt;/color&gt; sẽ hồi phục HP và &lt;color=Highlight&gt;greatly extends&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
+          <t>Kẻ địch này rất mạnh. &lt;color=Highlight&gt;Né thành công&lt;/color&gt; hoặc &lt;color=Highlight&gt;phản công&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách. &lt;color=Highlight&gt;Tiêu diệt kẻ địch&lt;/color&gt; sẽ hồi phục HP và &lt;color=Highlight&gt;kéo dài đáng kể&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;bị tấn công&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
         </is>
       </c>
     </row>
@@ -31441,7 +31441,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Challenge II: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
+          <t>Thử Thách II: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
         </is>
       </c>
     </row>
@@ -31571,7 +31571,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Kẻ địch này cực kỳ mạnh. &lt;color=Highlight&gt;Successful Dodges&lt;/color&gt; hoặc &lt;color=Highlight&gt;Counterattacks&lt;/color&gt; sẽ &lt;color=Highlight&gt;extend&lt;/color&gt; thời gian thử thách. &lt;color=Highlight&gt;Defeating enemies&lt;/color&gt; sẽ hồi phục HP và &lt;color=Highlight&gt;greatly extends&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
+          <t>Kẻ địch này cực kỳ mạnh. &lt;color=Highlight&gt;Né thành công&lt;/color&gt; hoặc &lt;color=Highlight&gt;phản công&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách. &lt;color=Highlight&gt;Tiêu diệt kẻ địch&lt;/color&gt; sẽ hồi phục HP và &lt;color=Highlight&gt;kéo dài đáng kể&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;bị tấn công&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
         </is>
       </c>
     </row>
@@ -31636,7 +31636,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Challenge III: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
+          <t>Thử Thách III: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
         </is>
       </c>
     </row>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>HP của kẻ địch sẽ hồi phục nếu không bị tấn công trong 5 giây. &lt;color=Highlight&gt;Successful Dodges&lt;/color&gt; hoặc sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;extends&lt;/color&gt; thời gian thử thách. Sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; sẽ &lt;color=Highlight&gt;extends&lt;/color&gt; thời gian thử thách và gây Aero DMG diện rộng, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ rút ngắn thời gian thử thách.</t>
+          <t>HP của kẻ địch sẽ hồi phục nếu không bị tấn công trong 5 giây. &lt;color=Highlight&gt;Né tránh thành công&lt;/color&gt; hoặc sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách. Sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách và gây Sát Thương Aero diện rộng, trong khi &lt;color=ThreatHigh&gt;nhận DMG&lt;/color&gt; sẽ rút ngắn thời gian thử thách.</t>
         </is>
       </c>
     </row>
@@ -31831,7 +31831,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Challenge I: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
+          <t>Thử Thách I: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
         </is>
       </c>
     </row>
@@ -31961,7 +31961,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Kẻ địch này rất mạnh. HP của kẻ địch sẽ hồi phục nếu không bị tấn công trong 5 giây. &lt;color=Highlight&gt;Successful Dodges&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;extends&lt;/color&gt; thời gian thử thách. Sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; sẽ &lt;color=Highlight&gt;extends&lt;/color&gt; thời gian thử thách và gây Aero DMG diện rộng, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
+          <t>Kẻ địch này rất mạnh. HP của kẻ địch sẽ hồi phục nếu không bị tấn công trong 5 giây. &lt;color=Highlight&gt;Né thành công&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách. Sử dụng &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách và gây DMG Aero diện rộng, trong khi &lt;color=ThreatHigh&gt;bị tấn công&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
         </is>
       </c>
     </row>
@@ -32026,7 +32026,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Challenge II: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
+          <t>Thử Thách II: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
         </is>
       </c>
     </row>
@@ -32156,7 +32156,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Kẻ địch này cực kỳ mạnh. HP của kẻ địch sẽ hồi phục nếu không bị tấn công trong 5 giây. &lt;color=Highlight&gt;Successful Dodges&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;extends&lt;/color&gt; thời gian thử thách. Sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; sẽ &lt;color=Highlight&gt;extends&lt;/color&gt; thời gian thử thách và gây Aero DMG diện rộng, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
+          <t>Kẻ địch này cực kỳ mạnh. HP của kẻ địch sẽ hồi phục nếu không bị tấn công trong 5 giây. &lt;color=Highlight&gt;Né thành công&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách. Sử dụng &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách và gây DMG Aero diện rộng, trong khi &lt;color=ThreatHigh&gt;bị tấn công&lt;/color&gt; sẽ làm giảm thời gian thử thách.</t>
         </is>
       </c>
     </row>
@@ -32221,7 +32221,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Challenge III: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
+          <t>Thử Thách III: Đánh bại tất cả đợt kẻ địch trong giấc mơ.</t>
         </is>
       </c>
     </row>
@@ -32286,7 +32286,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Kẻ địch này rất mạnh. Tấn công khi nó bị Hóa Đá sẽ gây thêm Electro DMG. &lt;color=Highlight&gt;Successful Dodges&lt;/color&gt;, &lt;color=Highlight&gt;Counterattacks&lt;/color&gt;, &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;extend&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ rút ngắn thời gian.</t>
+          <t>Kẻ địch này rất mạnh. Tấn công khi nó bị Hóa Đá sẽ gây thêm Sát Thương Electro. &lt;color=Highlight&gt;Né thành công&lt;/color&gt;, &lt;color=Highlight&gt;Phản Đòn&lt;/color&gt;, &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;bị DMG&lt;/color&gt; sẽ rút ngắn thời gian.</t>
         </is>
       </c>
     </row>
@@ -32351,7 +32351,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Kẻ địch này cực kỳ mạnh. Tấn công khi nó bị Hóa Đá sẽ gây thêm Electro DMG. &lt;color=Highlight&gt;Successful Dodges&lt;/color&gt;, &lt;color=Highlight&gt;Counterattacks&lt;/color&gt;, &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;extend&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ rút ngắn thời gian.</t>
+          <t>Kẻ địch này cực kỳ mạnh. Tấn công khi nó bị Hóa Đá sẽ gây thêm Sát Thương Electro. &lt;color=Highlight&gt;Né thành công&lt;/color&gt;, &lt;color=Highlight&gt;Phản công&lt;/color&gt;, &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;bị tấn công&lt;/color&gt; sẽ rút ngắn thời gian.</t>
         </is>
       </c>
     </row>
@@ -32416,7 +32416,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Kẻ địch này cực kỳ mạnh. Tấn công khi nó bị Hóa Đá sẽ gây thêm Electro DMG. &lt;color=Highlight&gt;Successful Dodges&lt;/color&gt;, &lt;color=Highlight&gt;Counterattacks&lt;/color&gt;, &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;extend&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;taking damage&lt;/color&gt; sẽ rút ngắn thời gian.</t>
+          <t>Kẻ địch này cực kỳ mạnh. Tấn công khi nó bị Hóa Đá sẽ gây thêm Sát Thương Electro. &lt;color=Highlight&gt;Né thành công&lt;/color&gt;, &lt;color=Highlight&gt;Phản công&lt;/color&gt;, &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=Highlight&gt;kéo dài&lt;/color&gt; thời gian thử thách, trong khi &lt;color=ThreatHigh&gt;bị tấn công&lt;/color&gt; sẽ rút ngắn thời gian.</t>
         </is>
       </c>
     </row>
@@ -32546,7 +32546,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Increase Tấn Công</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
     </row>
@@ -32611,7 +32611,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Biến Số Resonance</t>
+          <t>Biến Số Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Grapple, Cooldown chiêu của nó tạm thời bị loại bỏ trong {0} giây. Cooldown chiêu của hiệu ứng này là {1} giây.</t>
+          <t>Sau khi sử dụng Móc Câu, Thời gian hồi chiêu của nó tạm thời bị loại bỏ trong {0} giây. Thời gian hồi chiêu của hiệu ứng này là {1} giây.</t>
         </is>
       </c>
     </row>
@@ -32741,7 +32741,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Increase Sát Thương Basic Attack thêm {0} và Tốc Độ Basic Attack thêm {1}.</t>
+          <t>Tăng Sát Thương Basic Attack thêm {0} và Tốc Độ Basic Attack thêm {1}.</t>
         </is>
       </c>
     </row>
@@ -32806,7 +32806,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Khi Basic Attack hoặc các đòn được tính là Basic Attack gây sát thương, bỏ qua {0} Phòng Ngự của kẻ địch và hồi phục thêm STA.</t>
+          <t>Khi Đòn Basic Attack hoặc các đòn được tính là Đòn Basic Attack gây DMG, bỏ qua {0} Phòng Ngự của kẻ địch và hồi phục thêm STA.</t>
         </is>
       </c>
     </row>
@@ -32936,7 +32936,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Sử dụng Móc Neo hoặc kỹ năng Khởi Động tăng Tấn Công cho tất cả thành viên trong đội thêm {0}. Đồng thời, Tấn Công của Cyrospike Hoop do Wintry Variable triệu hồi cũng tăng thêm {1}, kéo dài {2} giây và chồng chất tối đa {3} lần.</t>
+          <t>Sử dụng Móc Neo hoặc kỹ năng Khởi Động tăng ATK cho tất cả thành viên trong đội thêm {0}. Đồng thời, ATK của Cyrospike Hoop do Wintry Variable triệu hồi cũng tăng thêm {1}, kéo dài {2} giây và chồng chất tối đa {3} lần.</t>
         </is>
       </c>
     </row>
@@ -33001,7 +33001,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Increase tốc độ di chuyển thêm {0}. Khi chạy nước rút, gây thêm sát thương nước rút trong {1} giây. Hiệu ứng này sẽ mất khi chuyển sang Resonator khác và có Cooldown chiêu {2} giây.</t>
+          <t>Tăng tốc độ di chuyển thêm {0}. Khi chạy nước rút, gây thêm DMG nước rút trong {1} giây. Hiệu ứng này sẽ mất khi chuyển sang Resonator khác và có Thời gian hồi chiêu {2} giây.</t>
         </is>
       </c>
     </row>
@@ -33066,7 +33066,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Liberation, cứ mỗi {1} giây trong {0} giây, một Tia Sét sẽ được triệu hồi khi tấn công trúng kẻ địch, gây Sát Thương Heavy Attack.</t>
+          <t>Sau khi sử dụng Resonance Liberation, cứ mỗi {1} giây trong {0} giây, một Tia Sét sẽ được triệu hồi khi tấn công trúng kẻ địch, gây Sát Thương Đòn Heavy Attack.</t>
         </is>
       </c>
     </row>
@@ -33131,7 +33131,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Khi Tấn Công Nặng hoặc các đòn tấn công được coi là Tấn Công Nặng gây sát thương, bỏ qua {0} DEF của kẻ địch và hồi phục thêm STA.</t>
+          <t>Khi Heavy Attack hoặc các đòn tấn công được coi là Heavy Attack gây DMG, bỏ qua {0} DEF của kẻ địch và hồi phục thêm STA.</t>
         </is>
       </c>
     </row>
@@ -33196,7 +33196,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Dodge tránh tăng Crit. Rate cho tất cả thành viên trong đội lên {0} và Crit. DMG lên {1}, hiệu ứng kéo dài {2} giây và có thể chồng chất tối đa {3} lần.</t>
+          <t>Né tránh tăng Crit. Rate cho tất cả thành viên trong đội lên {0} và Sát Thương Bạo Kích lên {1}, hiệu ứng kéo dài {2} giây và có thể chồng chất tối đa {3} lần.</t>
         </is>
       </c>
     </row>
@@ -33261,7 +33261,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Sau khi chạy nước rút trong 4s/8s/12s và dừng lại, Tấn Công của tất cả thành viên trong đội tăng 20%/40%/80% trong 15s, và Sát Thương Sét tăng 50%/100%/150%.</t>
+          <t>Sau khi chạy nước rút trong 4s/8s/12s và dừng lại, ATK của tất cả thành viên trong đội tăng 20%/40%/80% trong 15s, và Sát Thương Sét tăng 50%/100%/150%.</t>
         </is>
       </c>
     </row>
@@ -33326,7 +33326,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Basic Attack sẽ hồi phục thêm {0} Concerto Energy. Hiệu ứng này có thời gian Cooldown {1} giây.</t>
+          <t>Basic Attack sẽ hồi phục thêm {0} Concerto Energy. Hiệu ứng này có thời gian Hồi Chiêu {1} giây.</t>
         </is>
       </c>
     </row>
